--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-13</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -556,10 +556,10 @@
         <v>252</v>
       </c>
       <c r="N4" t="n">
-        <v>27000</v>
+        <v>27021.686746988</v>
       </c>
       <c r="O4" t="n">
-        <v>6804000</v>
+        <v>6809465.060240977</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -2419,10 +2419,10 @@
         <v>24</v>
       </c>
       <c r="N51" t="n">
-        <v>14857.623272727</v>
+        <v>14857.623287671</v>
       </c>
       <c r="O51" t="n">
-        <v>356582.958545448</v>
+        <v>356582.958904104</v>
       </c>
       <c r="P51" t="n">
         <v>34900</v>
@@ -4921,10 +4921,10 @@
         <v>3199</v>
       </c>
       <c r="N109" t="n">
-        <v>10600</v>
+        <v>10603.665283541</v>
       </c>
       <c r="O109" t="n">
-        <v>33909400</v>
+        <v>33921125.24204766</v>
       </c>
       <c r="P109" t="n">
         <v>17200</v>
@@ -4967,10 +4967,10 @@
         <v>1898</v>
       </c>
       <c r="N110" t="n">
-        <v>5216.8959816133</v>
+        <v>5216.8959810174</v>
       </c>
       <c r="O110" t="n">
-        <v>9901668.573102044</v>
+        <v>9901668.571971025</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
@@ -6193,10 +6193,10 @@
         <v>168</v>
       </c>
       <c r="N137" t="n">
-        <v>3594.2533147632</v>
+        <v>3596.7580209059</v>
       </c>
       <c r="O137" t="n">
-        <v>603834.5568802175</v>
+        <v>604255.3475121913</v>
       </c>
       <c r="P137" t="n">
         <v>6500</v>
@@ -6823,10 +6823,10 @@
         <v>809</v>
       </c>
       <c r="N151" t="n">
-        <v>4371.1712612367</v>
+        <v>4371.766707533</v>
       </c>
       <c r="O151" t="n">
-        <v>3536277.55034049</v>
+        <v>3536759.266394197</v>
       </c>
       <c r="P151" t="n">
         <v>8900</v>
@@ -7970,10 +7970,10 @@
         <v>4224</v>
       </c>
       <c r="N177" t="n">
-        <v>1550.1943880809</v>
+        <v>1550.1943922358</v>
       </c>
       <c r="O177" t="n">
-        <v>6548021.095253721</v>
+        <v>6548021.112804019</v>
       </c>
       <c r="P177" t="n">
         <v>2500</v>
@@ -8016,10 +8016,10 @@
         <v>1632</v>
       </c>
       <c r="N178" t="n">
-        <v>2403.5165803524</v>
+        <v>2403.5166025127</v>
       </c>
       <c r="O178" t="n">
-        <v>3922539.059135117</v>
+        <v>3922539.095300727</v>
       </c>
       <c r="P178" t="n">
         <v>3500</v>
@@ -16661,10 +16661,10 @@
         <v>4224</v>
       </c>
       <c r="N372" t="n">
-        <v>1516.0387548048</v>
+        <v>1516.0387544268</v>
       </c>
       <c r="O372" t="n">
-        <v>6403747.700295475</v>
+        <v>6403747.698698804</v>
       </c>
       <c r="P372" t="n">
         <v>2300</v>
@@ -16845,10 +16845,10 @@
         <v>720</v>
       </c>
       <c r="N376" t="n">
-        <v>2079.3834819145</v>
+        <v>2079.3834145441</v>
       </c>
       <c r="O376" t="n">
-        <v>1497156.10697844</v>
+        <v>1497156.058471752</v>
       </c>
       <c r="P376" t="n">
         <v>2900</v>
@@ -18454,10 +18454,10 @@
         <v>6996</v>
       </c>
       <c r="N411" t="n">
-        <v>517.2940518305199</v>
+        <v>517.72052761748</v>
       </c>
       <c r="O411" t="n">
-        <v>3618989.186606318</v>
+        <v>3621972.81121189</v>
       </c>
       <c r="P411" t="n">
         <v>900</v>
@@ -18586,10 +18586,10 @@
         <v>14792</v>
       </c>
       <c r="N414" t="n">
-        <v>703.79483731577</v>
+        <v>703.86725350482</v>
       </c>
       <c r="O414" t="n">
-        <v>10410533.23357487</v>
+        <v>10411604.4138433</v>
       </c>
       <c r="P414" t="n">
         <v>900</v>
@@ -19668,10 +19668,10 @@
         <v>4</v>
       </c>
       <c r="N438" t="n">
-        <v>1783.7988761992</v>
+        <v>1783.7988756856</v>
       </c>
       <c r="O438" t="n">
-        <v>7135.1955047968</v>
+        <v>7135.1955027424</v>
       </c>
       <c r="P438" t="n">
         <v>1500</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-14</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-15</t>
         </is>
       </c>
     </row>
@@ -556,10 +556,10 @@
         <v>252</v>
       </c>
       <c r="N4" t="n">
-        <v>27021.686746988</v>
+        <v>27000</v>
       </c>
       <c r="O4" t="n">
-        <v>6809465.060240977</v>
+        <v>6804000</v>
       </c>
       <c r="P4" t="n">
         <v>20000</v>
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3087824351</v>
+        <v>1811.3087912088</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.580838318</v>
+        <v>326035.582417584</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8550793651</v>
+        <v>6272.8550883392</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.697142862</v>
+        <v>1354936.699081267</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -2500,10 +2500,10 @@
         <v>52</v>
       </c>
       <c r="N53" t="n">
-        <v>16486.408</v>
+        <v>16486.40779661</v>
       </c>
       <c r="O53" t="n">
-        <v>857293.216</v>
+        <v>857293.2054237201</v>
       </c>
       <c r="P53" t="n">
         <v>30500</v>
@@ -2581,10 +2581,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>15711.964602273</v>
+        <v>15711.964444444</v>
       </c>
       <c r="O55" t="n">
-        <v>754174.3009091039</v>
+        <v>754174.293333312</v>
       </c>
       <c r="P55" t="n">
         <v>28500</v>
@@ -3103,10 +3103,10 @@
         <v>6</v>
       </c>
       <c r="N67" t="n">
-        <v>174389.81333333</v>
+        <v>174389.835</v>
       </c>
       <c r="O67" t="n">
-        <v>1046338.87999998</v>
+        <v>1046339.01</v>
       </c>
       <c r="P67" t="n">
         <v>368200</v>
@@ -3197,10 +3197,10 @@
         <v>15</v>
       </c>
       <c r="N69" t="n">
-        <v>344599.17851064</v>
+        <v>344599.17847826</v>
       </c>
       <c r="O69" t="n">
-        <v>5168987.6776596</v>
+        <v>5168987.6771739</v>
       </c>
       <c r="P69" t="n">
         <v>532900</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2551438323</v>
+        <v>2582.2551367187</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.555338884</v>
+        <v>2788835.547656196</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -4921,10 +4921,10 @@
         <v>3199</v>
       </c>
       <c r="N109" t="n">
-        <v>10603.665283541</v>
+        <v>10600</v>
       </c>
       <c r="O109" t="n">
-        <v>33921125.24204766</v>
+        <v>33909400</v>
       </c>
       <c r="P109" t="n">
         <v>17200</v>
@@ -4967,10 +4967,10 @@
         <v>1898</v>
       </c>
       <c r="N110" t="n">
-        <v>5216.8959810174</v>
+        <v>5216.895979825</v>
       </c>
       <c r="O110" t="n">
-        <v>9901668.571971025</v>
+        <v>9901668.56970785</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
@@ -5059,10 +5059,10 @@
         <v>6298</v>
       </c>
       <c r="N112" t="n">
-        <v>3158.8608348592</v>
+        <v>3158.8608362663</v>
       </c>
       <c r="O112" t="n">
-        <v>19894505.53794324</v>
+        <v>19894505.54680516</v>
       </c>
       <c r="P112" t="n">
         <v>5600</v>
@@ -5105,10 +5105,10 @@
         <v>144</v>
       </c>
       <c r="N113" t="n">
-        <v>3841.6250103093</v>
+        <v>3841.6250258532</v>
       </c>
       <c r="O113" t="n">
-        <v>553194.0014845391</v>
+        <v>553194.0037228608</v>
       </c>
       <c r="P113" t="n">
         <v>6900</v>
@@ -5197,10 +5197,10 @@
         <v>224</v>
       </c>
       <c r="N115" t="n">
-        <v>2694.823125</v>
+        <v>2694.8231119545</v>
       </c>
       <c r="O115" t="n">
-        <v>603640.38</v>
+        <v>603640.3770778079</v>
       </c>
       <c r="P115" t="n">
         <v>4900</v>
@@ -6193,10 +6193,10 @@
         <v>168</v>
       </c>
       <c r="N137" t="n">
-        <v>3596.7580209059</v>
+        <v>3594.2532489451</v>
       </c>
       <c r="O137" t="n">
-        <v>604255.3475121913</v>
+        <v>603834.5458227769</v>
       </c>
       <c r="P137" t="n">
         <v>6500</v>
@@ -6777,10 +6777,10 @@
         <v>78</v>
       </c>
       <c r="N150" t="n">
-        <v>3041.6600138793</v>
+        <v>3041.6600139179</v>
       </c>
       <c r="O150" t="n">
-        <v>237249.4810825854</v>
+        <v>237249.4810855962</v>
       </c>
       <c r="P150" t="n">
         <v>5500</v>
@@ -6823,10 +6823,10 @@
         <v>809</v>
       </c>
       <c r="N151" t="n">
-        <v>4371.766707533</v>
+        <v>4371.1712622683</v>
       </c>
       <c r="O151" t="n">
-        <v>3536759.266394197</v>
+        <v>3536277.551175055</v>
       </c>
       <c r="P151" t="n">
         <v>8900</v>
@@ -7742,10 +7742,10 @@
         <v>5338</v>
       </c>
       <c r="N172" t="n">
-        <v>1151.3923553227</v>
+        <v>1151.3923688623</v>
       </c>
       <c r="O172" t="n">
-        <v>6146132.392712573</v>
+        <v>6146132.464986957</v>
       </c>
       <c r="P172" t="n">
         <v>1500</v>
@@ -7878,10 +7878,10 @@
         <v>1152</v>
       </c>
       <c r="N175" t="n">
-        <v>1630.9242252747</v>
+        <v>1630.9242345815</v>
       </c>
       <c r="O175" t="n">
-        <v>1878824.707516454</v>
+        <v>1878824.718237888</v>
       </c>
       <c r="P175" t="n">
         <v>2500</v>
@@ -7924,10 +7924,10 @@
         <v>384</v>
       </c>
       <c r="N176" t="n">
-        <v>1690.5858435754</v>
+        <v>1690.5851822323</v>
       </c>
       <c r="O176" t="n">
-        <v>649184.9639329537</v>
+        <v>649184.7099772032</v>
       </c>
       <c r="P176" t="n">
         <v>2900</v>
@@ -7970,10 +7970,10 @@
         <v>4224</v>
       </c>
       <c r="N177" t="n">
-        <v>1550.1943922358</v>
+        <v>1550.19440684</v>
       </c>
       <c r="O177" t="n">
-        <v>6548021.112804019</v>
+        <v>6548021.17449216</v>
       </c>
       <c r="P177" t="n">
         <v>2500</v>
@@ -8016,10 +8016,10 @@
         <v>1632</v>
       </c>
       <c r="N178" t="n">
-        <v>2403.5166025127</v>
+        <v>2403.516914488</v>
       </c>
       <c r="O178" t="n">
-        <v>3922539.095300727</v>
+        <v>3922539.604444416</v>
       </c>
       <c r="P178" t="n">
         <v>3500</v>
@@ -10040,10 +10040,10 @@
         <v>150</v>
       </c>
       <c r="N225" t="n">
-        <v>4285.1961426844</v>
+        <v>4285.1961725395</v>
       </c>
       <c r="O225" t="n">
-        <v>642779.42140266</v>
+        <v>642779.425880925</v>
       </c>
       <c r="P225" t="n">
         <v>6900</v>
@@ -13174,10 +13174,10 @@
         <v>1145</v>
       </c>
       <c r="N296" t="n">
-        <v>1778.4727855775</v>
+        <v>1778.47280077</v>
       </c>
       <c r="O296" t="n">
-        <v>2036351.339486237</v>
+        <v>2036351.35688165</v>
       </c>
       <c r="P296" t="n">
         <v>4900</v>
@@ -16661,10 +16661,10 @@
         <v>4224</v>
       </c>
       <c r="N372" t="n">
-        <v>1516.0387544268</v>
+        <v>1516.0387516479</v>
       </c>
       <c r="O372" t="n">
-        <v>6403747.698698804</v>
+        <v>6403747.68696073</v>
       </c>
       <c r="P372" t="n">
         <v>2300</v>
@@ -16845,10 +16845,10 @@
         <v>720</v>
       </c>
       <c r="N376" t="n">
-        <v>2079.3834145441</v>
+        <v>2079.3834072432</v>
       </c>
       <c r="O376" t="n">
-        <v>1497156.058471752</v>
+        <v>1497156.053215104</v>
       </c>
       <c r="P376" t="n">
         <v>2900</v>
@@ -16891,10 +16891,10 @@
         <v>864</v>
       </c>
       <c r="N377" t="n">
-        <v>1803.0163011152</v>
+        <v>1803.0163058036</v>
       </c>
       <c r="O377" t="n">
-        <v>1557806.084163533</v>
+        <v>1557806.08821431</v>
       </c>
       <c r="P377" t="n">
         <v>2500</v>
@@ -17075,10 +17075,10 @@
         <v>864</v>
       </c>
       <c r="N381" t="n">
-        <v>1655.9297327394</v>
+        <v>1655.9297098214</v>
       </c>
       <c r="O381" t="n">
-        <v>1430723.289086842</v>
+        <v>1430723.26928569</v>
       </c>
       <c r="P381" t="n">
         <v>2500</v>
@@ -18454,10 +18454,10 @@
         <v>6996</v>
       </c>
       <c r="N411" t="n">
-        <v>517.72052761748</v>
+        <v>517.29416017244</v>
       </c>
       <c r="O411" t="n">
-        <v>3621972.81121189</v>
+        <v>3618989.94456639</v>
       </c>
       <c r="P411" t="n">
         <v>900</v>
@@ -18586,10 +18586,10 @@
         <v>14792</v>
       </c>
       <c r="N414" t="n">
-        <v>703.86725350482</v>
+        <v>703.79482873668</v>
       </c>
       <c r="O414" t="n">
-        <v>10411604.4138433</v>
+        <v>10410533.10667297</v>
       </c>
       <c r="P414" t="n">
         <v>900</v>
@@ -20040,10 +20040,10 @@
         <v>1976</v>
       </c>
       <c r="N446" t="n">
-        <v>7046.939827363</v>
+        <v>7046.9398272138</v>
       </c>
       <c r="O446" t="n">
-        <v>13924753.09886929</v>
+        <v>13924753.09857447</v>
       </c>
       <c r="P446" t="n">
         <v>9900</v>
@@ -21699,10 +21699,10 @@
         <v>1329</v>
       </c>
       <c r="N484" t="n">
-        <v>2523.3377457627</v>
+        <v>2523.3377451257</v>
       </c>
       <c r="O484" t="n">
-        <v>3353515.864118628</v>
+        <v>3353515.863272056</v>
       </c>
       <c r="P484" t="n">
         <v>2800</v>
@@ -21907,10 +21907,10 @@
         <v>427</v>
       </c>
       <c r="N489" t="n">
-        <v>3153.2320531758</v>
+        <v>3153.2320551996</v>
       </c>
       <c r="O489" t="n">
-        <v>1346430.086706067</v>
+        <v>1346430.087570229</v>
       </c>
       <c r="P489" t="n">
         <v>3300</v>
@@ -22392,10 +22392,10 @@
         <v>5</v>
       </c>
       <c r="N500" t="n">
-        <v>21664.371818182</v>
+        <v>21664.372</v>
       </c>
       <c r="O500" t="n">
-        <v>108321.85909091</v>
+        <v>108321.86</v>
       </c>
       <c r="P500" t="n">
         <v>30000</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -999,10 +999,10 @@
         <v>112</v>
       </c>
       <c r="N15" t="n">
-        <v>1990.0434548944</v>
+        <v>1990.0434042553</v>
       </c>
       <c r="O15" t="n">
-        <v>222884.8669481728</v>
+        <v>222884.8612765936</v>
       </c>
       <c r="P15" t="n">
         <v>4400</v>
@@ -3019,10 +3019,10 @@
         <v>108</v>
       </c>
       <c r="N65" t="n">
-        <v>141416.88462046</v>
+        <v>141885.15245033</v>
       </c>
       <c r="O65" t="n">
-        <v>15273023.53900968</v>
+        <v>15323596.46463564</v>
       </c>
       <c r="P65" t="n">
         <v>251900</v>
@@ -3061,10 +3061,10 @@
         <v>25</v>
       </c>
       <c r="N66" t="n">
-        <v>200072.20216981</v>
+        <v>201977.65171429</v>
       </c>
       <c r="O66" t="n">
-        <v>5001805.05424525</v>
+        <v>5049441.29285725</v>
       </c>
       <c r="P66" t="n">
         <v>312000</v>
@@ -3506,10 +3506,10 @@
         <v>85</v>
       </c>
       <c r="N76" t="n">
-        <v>61666.874171271</v>
+        <v>62706.203511236</v>
       </c>
       <c r="O76" t="n">
-        <v>5241684.304558035</v>
+        <v>5330027.29845506</v>
       </c>
       <c r="P76" t="n">
         <v>98900</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2551367187</v>
+        <v>2582.2551307749</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.547656196</v>
+        <v>2788835.541236892</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -7657,10 +7657,10 @@
         <v>505</v>
       </c>
       <c r="N170" t="n">
-        <v>11921.4</v>
+        <v>11949.761776368</v>
       </c>
       <c r="O170" t="n">
-        <v>6020307</v>
+        <v>6034629.69706584</v>
       </c>
       <c r="P170" t="n">
         <v>19900</v>
@@ -7878,10 +7878,10 @@
         <v>1152</v>
       </c>
       <c r="N175" t="n">
-        <v>1630.9242345815</v>
+        <v>1630.9242415885</v>
       </c>
       <c r="O175" t="n">
-        <v>1878824.718237888</v>
+        <v>1878824.726309952</v>
       </c>
       <c r="P175" t="n">
         <v>2500</v>
@@ -8016,10 +8016,10 @@
         <v>1632</v>
       </c>
       <c r="N178" t="n">
-        <v>2403.516914488</v>
+        <v>2403.5169237057</v>
       </c>
       <c r="O178" t="n">
-        <v>3922539.604444416</v>
+        <v>3922539.619487702</v>
       </c>
       <c r="P178" t="n">
         <v>3500</v>
@@ -11323,10 +11323,10 @@
         <v>30</v>
       </c>
       <c r="N255" t="n">
-        <v>16974.69</v>
+        <v>17078.829202454</v>
       </c>
       <c r="O255" t="n">
-        <v>509240.7</v>
+        <v>512364.8760736199</v>
       </c>
       <c r="P255" t="n">
         <v>26900</v>
@@ -12254,10 +12254,10 @@
         <v>399</v>
       </c>
       <c r="N276" t="n">
-        <v>5218.1705812417</v>
+        <v>5218.1705827815</v>
       </c>
       <c r="O276" t="n">
-        <v>2082050.061915438</v>
+        <v>2082050.062529819</v>
       </c>
       <c r="P276" t="n">
         <v>8500</v>
@@ -16661,10 +16661,10 @@
         <v>4224</v>
       </c>
       <c r="N372" t="n">
-        <v>1516.0387516479</v>
+        <v>1516.0387513947</v>
       </c>
       <c r="O372" t="n">
-        <v>6403747.68696073</v>
+        <v>6403747.685891213</v>
       </c>
       <c r="P372" t="n">
         <v>2300</v>
@@ -18454,10 +18454,10 @@
         <v>6996</v>
       </c>
       <c r="N411" t="n">
-        <v>517.29416017244</v>
+        <v>517.81142476254</v>
       </c>
       <c r="O411" t="n">
-        <v>3618989.94456639</v>
+        <v>3622608.72763873</v>
       </c>
       <c r="P411" t="n">
         <v>900</v>
@@ -18586,10 +18586,10 @@
         <v>14792</v>
       </c>
       <c r="N414" t="n">
-        <v>703.79482873668</v>
+        <v>703.79482793718</v>
       </c>
       <c r="O414" t="n">
-        <v>10410533.10667297</v>
+        <v>10410533.09484677</v>
       </c>
       <c r="P414" t="n">
         <v>900</v>
@@ -21394,10 +21394,10 @@
         <v>78</v>
       </c>
       <c r="N477" t="n">
-        <v>3181.9</v>
+        <v>3248.0517671518</v>
       </c>
       <c r="O477" t="n">
-        <v>248188.2</v>
+        <v>253348.0378378404</v>
       </c>
       <c r="P477" t="n">
         <v>5100</v>
@@ -22346,10 +22346,10 @@
         <v>60</v>
       </c>
       <c r="N499" t="n">
-        <v>1952.66</v>
+        <v>1991.055</v>
       </c>
       <c r="O499" t="n">
-        <v>117159.6</v>
+        <v>119463.3</v>
       </c>
       <c r="P499" t="n">
         <v>3500</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3087912088</v>
+        <v>1811.3088176353</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.582417584</v>
+        <v>326035.587174354</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -2500,10 +2500,10 @@
         <v>52</v>
       </c>
       <c r="N53" t="n">
-        <v>16486.407586207</v>
+        <v>16486.407256637</v>
       </c>
       <c r="O53" t="n">
-        <v>857293.1944827639</v>
+        <v>857293.1773451241</v>
       </c>
       <c r="P53" t="n">
         <v>30500</v>
@@ -2675,10 +2675,10 @@
         <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>13712.84</v>
+        <v>13712.837142857</v>
       </c>
       <c r="O57" t="n">
-        <v>27425.68</v>
+        <v>27425.674285714</v>
       </c>
       <c r="P57" t="n">
         <v>22600</v>
@@ -5059,10 +5059,10 @@
         <v>6298</v>
       </c>
       <c r="N112" t="n">
-        <v>3158.8608362663</v>
+        <v>3158.8608369301</v>
       </c>
       <c r="O112" t="n">
-        <v>19894505.54680516</v>
+        <v>19894505.55098577</v>
       </c>
       <c r="P112" t="n">
         <v>5600</v>
@@ -5471,10 +5471,10 @@
         <v>3024</v>
       </c>
       <c r="N121" t="n">
-        <v>3795.7100076147</v>
+        <v>3795.7100076161</v>
       </c>
       <c r="O121" t="n">
-        <v>11478227.06302685</v>
+        <v>11478227.06303109</v>
       </c>
       <c r="P121" t="n">
         <v>6200</v>
@@ -5791,10 +5791,10 @@
         <v>24</v>
       </c>
       <c r="N128" t="n">
-        <v>2267.0481062554</v>
+        <v>2267.0481021898</v>
       </c>
       <c r="O128" t="n">
-        <v>54409.1545501296</v>
+        <v>54409.1544525552</v>
       </c>
       <c r="P128" t="n">
         <v>3900</v>
@@ -7970,10 +7970,10 @@
         <v>3744</v>
       </c>
       <c r="N177" t="n">
-        <v>1550.1944427152</v>
+        <v>1550.1944587288</v>
       </c>
       <c r="O177" t="n">
-        <v>5803927.993525709</v>
+        <v>5803928.053480628</v>
       </c>
       <c r="P177" t="n">
         <v>2500</v>
@@ -8016,10 +8016,10 @@
         <v>1248</v>
       </c>
       <c r="N178" t="n">
-        <v>2403.5172431982</v>
+        <v>2403.5172815804</v>
       </c>
       <c r="O178" t="n">
-        <v>2999589.519511354</v>
+        <v>2999589.567412339</v>
       </c>
       <c r="P178" t="n">
         <v>3500</v>
@@ -10688,10 +10688,10 @@
         <v>95</v>
       </c>
       <c r="N240" t="n">
-        <v>12005.15982684</v>
+        <v>12005.159823789</v>
       </c>
       <c r="O240" t="n">
-        <v>1140490.1835498</v>
+        <v>1140490.183259955</v>
       </c>
       <c r="P240" t="n">
         <v>19500</v>
@@ -16712,10 +16712,10 @@
         <v>4224</v>
       </c>
       <c r="N373" t="n">
-        <v>1516.0387513947</v>
+        <v>1516.0387508879</v>
       </c>
       <c r="O373" t="n">
-        <v>6403747.685891213</v>
+        <v>6403747.68375049</v>
       </c>
       <c r="P373" t="n">
         <v>2300</v>
@@ -16942,10 +16942,10 @@
         <v>672</v>
       </c>
       <c r="N378" t="n">
-        <v>1803.0164892802</v>
+        <v>1803.016504221</v>
       </c>
       <c r="O378" t="n">
-        <v>1211627.080796294</v>
+        <v>1211627.090836512</v>
       </c>
       <c r="P378" t="n">
         <v>2500</v>
@@ -17034,10 +17034,10 @@
         <v>396</v>
       </c>
       <c r="N380" t="n">
-        <v>2056.0823128492</v>
+        <v>2056.0822725571</v>
       </c>
       <c r="O380" t="n">
-        <v>814208.5958882833</v>
+        <v>814208.5799326117</v>
       </c>
       <c r="P380" t="n">
         <v>2900</v>
@@ -18750,10 +18750,10 @@
         <v>5844</v>
       </c>
       <c r="N417" t="n">
-        <v>517.29429288703</v>
+        <v>517.29430006698</v>
       </c>
       <c r="O417" t="n">
-        <v>3023067.847631803</v>
+        <v>3023067.889591431</v>
       </c>
       <c r="P417" t="n">
         <v>900</v>
@@ -19964,10 +19964,10 @@
         <v>4</v>
       </c>
       <c r="N444" t="n">
-        <v>1783.7988736264</v>
+        <v>1783.7988731104</v>
       </c>
       <c r="O444" t="n">
-        <v>7135.1954945056</v>
+        <v>7135.1954924416</v>
       </c>
       <c r="P444" t="n">
         <v>1500</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-16</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3088176353</v>
+        <v>1811.3089521872</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.587174354</v>
+        <v>326035.611393696</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1951,10 +1951,10 @@
         <v>527</v>
       </c>
       <c r="N39" t="n">
-        <v>2413.0010952903</v>
+        <v>2413.0010989011</v>
       </c>
       <c r="O39" t="n">
-        <v>1271651.577217988</v>
+        <v>1271651.57912088</v>
       </c>
       <c r="P39" t="n">
         <v>4700</v>
@@ -2458,10 +2458,10 @@
         <v>152</v>
       </c>
       <c r="N52" t="n">
-        <v>3910.6279405034</v>
+        <v>3910.6279357798</v>
       </c>
       <c r="O52" t="n">
-        <v>594415.4469565168</v>
+        <v>594415.4462385295</v>
       </c>
       <c r="P52" t="n">
         <v>9100</v>
@@ -2581,10 +2581,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>15711.964345238</v>
+        <v>15711.964411765</v>
       </c>
       <c r="O55" t="n">
-        <v>754174.2885714241</v>
+        <v>754174.29176472</v>
       </c>
       <c r="P55" t="n">
         <v>28500</v>
@@ -2628,10 +2628,10 @@
         <v>48</v>
       </c>
       <c r="N56" t="n">
-        <v>30238.813461538</v>
+        <v>30238.813396226</v>
       </c>
       <c r="O56" t="n">
-        <v>1451463.046153824</v>
+        <v>1451463.043018848</v>
       </c>
       <c r="P56" t="n">
         <v>51100</v>
@@ -2675,10 +2675,10 @@
         <v>2</v>
       </c>
       <c r="N57" t="n">
-        <v>13712.837142857</v>
+        <v>13712.838181818</v>
       </c>
       <c r="O57" t="n">
-        <v>27425.674285714</v>
+        <v>27425.676363636</v>
       </c>
       <c r="P57" t="n">
         <v>22600</v>
@@ -2878,10 +2878,10 @@
         <v>20</v>
       </c>
       <c r="N62" t="n">
-        <v>56906.807619048</v>
+        <v>56906.80804878</v>
       </c>
       <c r="O62" t="n">
-        <v>1138136.15238096</v>
+        <v>1138136.1609756</v>
       </c>
       <c r="P62" t="n">
         <v>95900</v>
@@ -3150,10 +3150,10 @@
         <v>16</v>
       </c>
       <c r="N68" t="n">
-        <v>251809.29259259</v>
+        <v>251809.29230769</v>
       </c>
       <c r="O68" t="n">
-        <v>4028948.68148144</v>
+        <v>4028948.67692304</v>
       </c>
       <c r="P68" t="n">
         <v>584000</v>
@@ -3892,10 +3892,10 @@
         <v>960</v>
       </c>
       <c r="N85" t="n">
-        <v>1950.2140408627</v>
+        <v>1950.2139862543</v>
       </c>
       <c r="O85" t="n">
-        <v>1872205.479228192</v>
+        <v>1872205.426804128</v>
       </c>
       <c r="P85" t="n">
         <v>2900</v>
@@ -4020,10 +4020,10 @@
         <v>200</v>
       </c>
       <c r="N88" t="n">
-        <v>4937.3101659125</v>
+        <v>4937.3101654135</v>
       </c>
       <c r="O88" t="n">
-        <v>987462.0331825</v>
+        <v>987462.0330827</v>
       </c>
       <c r="P88" t="n">
         <v>7500</v>
@@ -4696,10 +4696,10 @@
         <v>34</v>
       </c>
       <c r="N104" t="n">
-        <v>18694.410088692</v>
+        <v>18694.410088889</v>
       </c>
       <c r="O104" t="n">
-        <v>635609.9430155279</v>
+        <v>635609.943022226</v>
       </c>
       <c r="P104" t="n">
         <v>29900</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2550693069</v>
+        <v>2582.2550509317</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.474851452</v>
+        <v>2788835.455006236</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -4967,10 +4967,10 @@
         <v>1898</v>
       </c>
       <c r="N110" t="n">
-        <v>5216.8959750483</v>
+        <v>5216.8959642591</v>
       </c>
       <c r="O110" t="n">
-        <v>9901668.560641672</v>
+        <v>9901668.540163772</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
@@ -5059,10 +5059,10 @@
         <v>6298</v>
       </c>
       <c r="N112" t="n">
-        <v>3158.8608369301</v>
+        <v>3158.8608375534</v>
       </c>
       <c r="O112" t="n">
-        <v>19894505.55098577</v>
+        <v>19894505.55491131</v>
       </c>
       <c r="P112" t="n">
         <v>5600</v>
@@ -5105,10 +5105,10 @@
         <v>144</v>
       </c>
       <c r="N113" t="n">
-        <v>3841.6250258532</v>
+        <v>3841.6250362694</v>
       </c>
       <c r="O113" t="n">
-        <v>553194.0037228608</v>
+        <v>553194.0052227936</v>
       </c>
       <c r="P113" t="n">
         <v>6900</v>
@@ -5197,10 +5197,10 @@
         <v>224</v>
       </c>
       <c r="N115" t="n">
-        <v>2694.8231119545</v>
+        <v>2694.8230922931</v>
       </c>
       <c r="O115" t="n">
-        <v>603640.3770778079</v>
+        <v>603640.3726736545</v>
       </c>
       <c r="P115" t="n">
         <v>4900</v>
@@ -5791,10 +5791,10 @@
         <v>24</v>
       </c>
       <c r="N128" t="n">
-        <v>2267.0481021898</v>
+        <v>2267.0481062554</v>
       </c>
       <c r="O128" t="n">
-        <v>54409.1544525552</v>
+        <v>54409.1545501296</v>
       </c>
       <c r="P128" t="n">
         <v>3900</v>
@@ -5912,7 +5912,7 @@
         </is>
       </c>
       <c r="J131" t="n">
-        <v>80</v>
+        <v>5080</v>
       </c>
       <c r="K131" t="n">
         <v>0</v>
@@ -5921,19 +5921,19 @@
         <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>80</v>
+        <v>5080</v>
       </c>
       <c r="N131" t="n">
         <v>156</v>
       </c>
       <c r="O131" t="n">
-        <v>12480</v>
+        <v>792480</v>
       </c>
       <c r="P131" t="n">
         <v>195</v>
       </c>
       <c r="Q131" t="n">
-        <v>15600</v>
+        <v>990600</v>
       </c>
     </row>
     <row r="132">
@@ -6147,10 +6147,10 @@
         <v>168</v>
       </c>
       <c r="N136" t="n">
-        <v>3594.2532155477</v>
+        <v>3594.2531526391</v>
       </c>
       <c r="O136" t="n">
-        <v>603834.5402120136</v>
+        <v>603834.5296433688</v>
       </c>
       <c r="P136" t="n">
         <v>6500</v>
@@ -6372,10 +6372,10 @@
         <v>361</v>
       </c>
       <c r="N141" t="n">
-        <v>14822.378829268</v>
+        <v>14822.378827839</v>
       </c>
       <c r="O141" t="n">
-        <v>5350878.757365748</v>
+        <v>5350878.756849879</v>
       </c>
       <c r="P141" t="n">
         <v>24900</v>
@@ -6594,10 +6594,10 @@
         <v>912</v>
       </c>
       <c r="N146" t="n">
-        <v>12422.462940415</v>
+        <v>12422.462941685</v>
       </c>
       <c r="O146" t="n">
-        <v>11329286.20165848</v>
+        <v>11329286.20281672</v>
       </c>
       <c r="P146" t="n">
         <v>19900</v>
@@ -6823,10 +6823,10 @@
         <v>78</v>
       </c>
       <c r="N151" t="n">
-        <v>3041.660013947</v>
+        <v>3041.6600139665</v>
       </c>
       <c r="O151" t="n">
-        <v>237249.481087866</v>
+        <v>237249.481089387</v>
       </c>
       <c r="P151" t="n">
         <v>5500</v>
@@ -6869,10 +6869,10 @@
         <v>809</v>
       </c>
       <c r="N152" t="n">
-        <v>4371.1712623543</v>
+        <v>4371.1712626125</v>
       </c>
       <c r="O152" t="n">
-        <v>3536277.551244629</v>
+        <v>3536277.551453513</v>
       </c>
       <c r="P152" t="n">
         <v>8900</v>
@@ -7172,10 +7172,10 @@
         <v>10357</v>
       </c>
       <c r="N159" t="n">
-        <v>1532.6290255288</v>
+        <v>1532.6290251022</v>
       </c>
       <c r="O159" t="n">
-        <v>15873438.81740178</v>
+        <v>15873438.81298349</v>
       </c>
       <c r="P159" t="n">
         <v>1200</v>
@@ -7924,10 +7924,10 @@
         <v>768</v>
       </c>
       <c r="N176" t="n">
-        <v>1630.9242710358</v>
+        <v>1630.9243202247</v>
       </c>
       <c r="O176" t="n">
-        <v>1252549.840155494</v>
+        <v>1252549.87793257</v>
       </c>
       <c r="P176" t="n">
         <v>2500</v>
@@ -7970,10 +7970,10 @@
         <v>3744</v>
       </c>
       <c r="N177" t="n">
-        <v>1550.1944587288</v>
+        <v>1550.1945107573</v>
       </c>
       <c r="O177" t="n">
-        <v>5803928.053480628</v>
+        <v>5803928.248275331</v>
       </c>
       <c r="P177" t="n">
         <v>2500</v>
@@ -8016,10 +8016,10 @@
         <v>1248</v>
       </c>
       <c r="N178" t="n">
-        <v>2403.5172815804</v>
+        <v>2403.5178067661</v>
       </c>
       <c r="O178" t="n">
-        <v>2999589.567412339</v>
+        <v>2999590.222844093</v>
       </c>
       <c r="P178" t="n">
         <v>3500</v>
@@ -9520,10 +9520,10 @@
         <v>381</v>
       </c>
       <c r="N213" t="n">
-        <v>2680.7396945137</v>
+        <v>2680.7396939413</v>
       </c>
       <c r="O213" t="n">
-        <v>1021361.82360972</v>
+        <v>1021361.823391635</v>
       </c>
       <c r="P213" t="n">
         <v>4900</v>
@@ -9561,10 +9561,10 @@
         <v>1254</v>
       </c>
       <c r="N214" t="n">
-        <v>880.32978266178</v>
+        <v>880.3298042095</v>
       </c>
       <c r="O214" t="n">
-        <v>1103933.547457872</v>
+        <v>1103933.574478713</v>
       </c>
       <c r="P214" t="n">
         <v>1200</v>
@@ -10045,10 +10045,10 @@
         <v>150</v>
       </c>
       <c r="N225" t="n">
-        <v>4285.1962026862</v>
+        <v>4285.1962331288</v>
       </c>
       <c r="O225" t="n">
-        <v>642779.43040293</v>
+        <v>642779.43496932</v>
       </c>
       <c r="P225" t="n">
         <v>6900</v>
@@ -11328,10 +11328,10 @@
         <v>34</v>
       </c>
       <c r="N255" t="n">
-        <v>27123.764869739</v>
+        <v>27123.764849095</v>
       </c>
       <c r="O255" t="n">
-        <v>922208.005571126</v>
+        <v>922208.0048692301</v>
       </c>
       <c r="P255" t="n">
         <v>44500</v>
@@ -11937,10 +11937,10 @@
         <v>487</v>
       </c>
       <c r="N269" t="n">
-        <v>3113.8900282885</v>
+        <v>3113.8900281294</v>
       </c>
       <c r="O269" t="n">
-        <v>1516464.443776499</v>
+        <v>1516464.443699018</v>
       </c>
       <c r="P269" t="n">
         <v>5000</v>
@@ -12121,10 +12121,10 @@
         <v>69</v>
       </c>
       <c r="N273" t="n">
-        <v>4163.1602247191</v>
+        <v>4163.160212766</v>
       </c>
       <c r="O273" t="n">
-        <v>287258.0555056179</v>
+        <v>287258.054680854</v>
       </c>
       <c r="P273" t="n">
         <v>6700</v>
@@ -12305,10 +12305,10 @@
         <v>399</v>
       </c>
       <c r="N277" t="n">
-        <v>5218.1705827815</v>
+        <v>5218.1705835544</v>
       </c>
       <c r="O277" t="n">
-        <v>2082050.062529819</v>
+        <v>2082050.062838206</v>
       </c>
       <c r="P277" t="n">
         <v>8500</v>
@@ -13225,10 +13225,10 @@
         <v>1145</v>
       </c>
       <c r="N297" t="n">
-        <v>1778.47280077</v>
+        <v>1778.4728156749</v>
       </c>
       <c r="O297" t="n">
-        <v>2036351.35688165</v>
+        <v>2036351.373947761</v>
       </c>
       <c r="P297" t="n">
         <v>4900</v>
@@ -14007,10 +14007,10 @@
         <v>28</v>
       </c>
       <c r="N314" t="n">
-        <v>2252.2979080119</v>
+        <v>2252.2979790419</v>
       </c>
       <c r="O314" t="n">
-        <v>63064.34142433319</v>
+        <v>63064.3434131732</v>
       </c>
       <c r="P314" t="n">
         <v>3900</v>
@@ -16712,10 +16712,10 @@
         <v>4224</v>
       </c>
       <c r="N373" t="n">
-        <v>1516.0387508879</v>
+        <v>1516.0387464358</v>
       </c>
       <c r="O373" t="n">
-        <v>6403747.68375049</v>
+        <v>6403747.664944819</v>
       </c>
       <c r="P373" t="n">
         <v>2300</v>
@@ -16758,10 +16758,10 @@
         <v>288</v>
       </c>
       <c r="N374" t="n">
-        <v>2458.5126313933</v>
+        <v>2458.5126157653</v>
       </c>
       <c r="O374" t="n">
-        <v>708051.6378412704</v>
+        <v>708051.6333404063</v>
       </c>
       <c r="P374" t="n">
         <v>3500</v>
@@ -16804,10 +16804,10 @@
         <v>240</v>
       </c>
       <c r="N375" t="n">
-        <v>1907.3925257143</v>
+        <v>1907.3925085911</v>
       </c>
       <c r="O375" t="n">
-        <v>457774.206171432</v>
+        <v>457774.202061864</v>
       </c>
       <c r="P375" t="n">
         <v>2500</v>
@@ -16850,10 +16850,10 @@
         <v>288</v>
       </c>
       <c r="N376" t="n">
-        <v>1771.0894375457</v>
+        <v>1771.089398827</v>
       </c>
       <c r="O376" t="n">
-        <v>510073.7580131616</v>
+        <v>510073.746862176</v>
       </c>
       <c r="P376" t="n">
         <v>2500</v>
@@ -16896,10 +16896,10 @@
         <v>720</v>
       </c>
       <c r="N377" t="n">
-        <v>2079.3833876946</v>
+        <v>2079.3833258511</v>
       </c>
       <c r="O377" t="n">
-        <v>1497156.039140112</v>
+        <v>1497155.994612792</v>
       </c>
       <c r="P377" t="n">
         <v>2900</v>
@@ -16942,10 +16942,10 @@
         <v>672</v>
       </c>
       <c r="N378" t="n">
-        <v>1803.016504221</v>
+        <v>1803.0166107644</v>
       </c>
       <c r="O378" t="n">
-        <v>1211627.090836512</v>
+        <v>1211627.162433677</v>
       </c>
       <c r="P378" t="n">
         <v>2500</v>
@@ -16988,10 +16988,10 @@
         <v>1440</v>
       </c>
       <c r="N379" t="n">
-        <v>2122.1635338843</v>
+        <v>2122.1635296064</v>
       </c>
       <c r="O379" t="n">
-        <v>3055915.488793392</v>
+        <v>3055915.482633216</v>
       </c>
       <c r="P379" t="n">
         <v>2900</v>
@@ -17034,10 +17034,10 @@
         <v>396</v>
       </c>
       <c r="N380" t="n">
-        <v>2056.0822725571</v>
+        <v>2056.0822493428</v>
       </c>
       <c r="O380" t="n">
-        <v>814208.5799326117</v>
+        <v>814208.5707397488</v>
       </c>
       <c r="P380" t="n">
         <v>2900</v>
@@ -17080,10 +17080,10 @@
         <v>714</v>
       </c>
       <c r="N381" t="n">
-        <v>3224.5693815514</v>
+        <v>3224.5693864709</v>
       </c>
       <c r="O381" t="n">
-        <v>2302342.5384277</v>
+        <v>2302342.541940222</v>
       </c>
       <c r="P381" t="n">
         <v>4500</v>
@@ -17126,10 +17126,10 @@
         <v>864</v>
       </c>
       <c r="N382" t="n">
-        <v>1655.9297098214</v>
+        <v>1655.9295385779</v>
       </c>
       <c r="O382" t="n">
-        <v>1430723.26928569</v>
+        <v>1430723.121331306</v>
       </c>
       <c r="P382" t="n">
         <v>2500</v>
@@ -18394,10 +18394,10 @@
         <v>17</v>
       </c>
       <c r="N409" t="n">
-        <v>2286.1645384615</v>
+        <v>2286.1645279383</v>
       </c>
       <c r="O409" t="n">
-        <v>38864.79715384549</v>
+        <v>38864.7969749511</v>
       </c>
       <c r="P409" t="n">
         <v>3000</v>
@@ -18750,10 +18750,10 @@
         <v>5844</v>
       </c>
       <c r="N417" t="n">
-        <v>517.29430006698</v>
+        <v>517.2943625967</v>
       </c>
       <c r="O417" t="n">
-        <v>3023067.889591431</v>
+        <v>3023068.255015115</v>
       </c>
       <c r="P417" t="n">
         <v>900</v>
@@ -18882,10 +18882,10 @@
         <v>14791</v>
       </c>
       <c r="N420" t="n">
-        <v>703.79482106458</v>
+        <v>703.79481075491</v>
       </c>
       <c r="O420" t="n">
-        <v>10409829.1983662</v>
+        <v>10409829.04587587</v>
       </c>
       <c r="P420" t="n">
         <v>900</v>
@@ -18931,10 +18931,10 @@
         <v>127</v>
       </c>
       <c r="N421" t="n">
-        <v>3182.2511257036</v>
+        <v>3182.2511299435</v>
       </c>
       <c r="O421" t="n">
-        <v>404145.8929643572</v>
+        <v>404145.8935028245</v>
       </c>
       <c r="P421" t="n">
         <v>6900</v>
@@ -20925,10 +20925,10 @@
         <v>20</v>
       </c>
       <c r="N465" t="n">
-        <v>1619.5682224532</v>
+        <v>1619.5682206035</v>
       </c>
       <c r="O465" t="n">
-        <v>32391.364449064</v>
+        <v>32391.36441207</v>
       </c>
       <c r="P465" t="n">
         <v>1900</v>
@@ -22373,10 +22373,10 @@
         <v>1</v>
       </c>
       <c r="N499" t="n">
-        <v>4985.4066666667</v>
+        <v>4985.4069767442</v>
       </c>
       <c r="O499" t="n">
-        <v>4985.4066666667</v>
+        <v>4985.4069767442</v>
       </c>
       <c r="P499" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -1155,10 +1155,10 @@
         <v>401</v>
       </c>
       <c r="N19" t="n">
-        <v>4072</v>
+        <v>4088.8962655602</v>
       </c>
       <c r="O19" t="n">
-        <v>1632872</v>
+        <v>1639647.40248964</v>
       </c>
       <c r="P19" t="n">
         <v>7500</v>
@@ -2500,10 +2500,10 @@
         <v>52</v>
       </c>
       <c r="N53" t="n">
-        <v>16486.407256637</v>
+        <v>16486.407142857</v>
       </c>
       <c r="O53" t="n">
-        <v>857293.1773451241</v>
+        <v>857293.1714285639</v>
       </c>
       <c r="P53" t="n">
         <v>30500</v>
@@ -3892,10 +3892,10 @@
         <v>960</v>
       </c>
       <c r="N85" t="n">
-        <v>1950.2139862543</v>
+        <v>1950.2139585731</v>
       </c>
       <c r="O85" t="n">
-        <v>1872205.426804128</v>
+        <v>1872205.400230176</v>
       </c>
       <c r="P85" t="n">
         <v>2900</v>
@@ -4020,10 +4020,10 @@
         <v>200</v>
       </c>
       <c r="N88" t="n">
-        <v>4937.3101654135</v>
+        <v>4937.310165538</v>
       </c>
       <c r="O88" t="n">
-        <v>987462.0330827</v>
+        <v>987462.0331075999</v>
       </c>
       <c r="P88" t="n">
         <v>7500</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2550509317</v>
+        <v>2582.2550435432</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.455006236</v>
+        <v>2788835.447026656</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -4967,10 +4967,10 @@
         <v>1898</v>
       </c>
       <c r="N110" t="n">
-        <v>5216.8959642591</v>
+        <v>5220.0054239309</v>
       </c>
       <c r="O110" t="n">
-        <v>9901668.540163772</v>
+        <v>9907570.294620849</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
@@ -5384,10 +5384,10 @@
         <v>1081</v>
       </c>
       <c r="N119" t="n">
-        <v>6507</v>
+        <v>6513.4596293845</v>
       </c>
       <c r="O119" t="n">
-        <v>7034067</v>
+        <v>7041049.859364645</v>
       </c>
       <c r="P119" t="n">
         <v>9900</v>
@@ -5970,10 +5970,10 @@
         <v>501</v>
       </c>
       <c r="N132" t="n">
-        <v>8662</v>
+        <v>8680.102403343801</v>
       </c>
       <c r="O132" t="n">
-        <v>4339662</v>
+        <v>4348731.304075244</v>
       </c>
       <c r="P132" t="n">
         <v>14200</v>
@@ -6147,10 +6147,10 @@
         <v>168</v>
       </c>
       <c r="N136" t="n">
-        <v>3594.2531526391</v>
+        <v>3594.2531477516</v>
       </c>
       <c r="O136" t="n">
-        <v>603834.5296433688</v>
+        <v>603834.5288222688</v>
       </c>
       <c r="P136" t="n">
         <v>6500</v>
@@ -6372,10 +6372,10 @@
         <v>361</v>
       </c>
       <c r="N141" t="n">
-        <v>14822.378827839</v>
+        <v>14840.499095355</v>
       </c>
       <c r="O141" t="n">
-        <v>5350878.756849879</v>
+        <v>5357420.173423155</v>
       </c>
       <c r="P141" t="n">
         <v>24900</v>
@@ -6548,10 +6548,10 @@
         <v>180</v>
       </c>
       <c r="N145" t="n">
-        <v>2665.4</v>
+        <v>2668.7380087664</v>
       </c>
       <c r="O145" t="n">
-        <v>479772</v>
+        <v>480372.841577952</v>
       </c>
       <c r="P145" t="n">
         <v>20900</v>
@@ -6730,10 +6730,10 @@
         <v>5040</v>
       </c>
       <c r="N149" t="n">
-        <v>3472.2761671707</v>
+        <v>3490.9933434692</v>
       </c>
       <c r="O149" t="n">
-        <v>17500271.88254033</v>
+        <v>17594606.45108477</v>
       </c>
       <c r="P149" t="n">
         <v>5900</v>
@@ -7878,10 +7878,10 @@
         <v>457</v>
       </c>
       <c r="N175" t="n">
-        <v>9903</v>
+        <v>9918.473437500001</v>
       </c>
       <c r="O175" t="n">
-        <v>4525671</v>
+        <v>4532742.3609375</v>
       </c>
       <c r="P175" t="n">
         <v>15900</v>
@@ -7924,10 +7924,10 @@
         <v>768</v>
       </c>
       <c r="N176" t="n">
-        <v>1630.9243202247</v>
+        <v>1630.9243287363</v>
       </c>
       <c r="O176" t="n">
-        <v>1252549.87793257</v>
+        <v>1252549.884469478</v>
       </c>
       <c r="P176" t="n">
         <v>2500</v>
@@ -7970,10 +7970,10 @@
         <v>3744</v>
       </c>
       <c r="N177" t="n">
-        <v>1550.1945107573</v>
+        <v>1550.1945200974</v>
       </c>
       <c r="O177" t="n">
-        <v>5803928.248275331</v>
+        <v>5803928.283244666</v>
       </c>
       <c r="P177" t="n">
         <v>2500</v>
@@ -8016,10 +8016,10 @@
         <v>1248</v>
       </c>
       <c r="N178" t="n">
-        <v>2403.5178067661</v>
+        <v>2403.5178733813</v>
       </c>
       <c r="O178" t="n">
-        <v>2999590.222844093</v>
+        <v>2999590.305979862</v>
       </c>
       <c r="P178" t="n">
         <v>3500</v>
@@ -10555,10 +10555,10 @@
         <v>2160</v>
       </c>
       <c r="N237" t="n">
-        <v>4814.2679269747</v>
+        <v>4817.516083662</v>
       </c>
       <c r="O237" t="n">
-        <v>10398818.72226535</v>
+        <v>10405834.74070992</v>
       </c>
       <c r="P237" t="n">
         <v>9900</v>
@@ -10642,10 +10642,10 @@
         <v>150</v>
       </c>
       <c r="N239" t="n">
-        <v>11562.038418079</v>
+        <v>11660.859259259</v>
       </c>
       <c r="O239" t="n">
-        <v>1734305.76271185</v>
+        <v>1749128.88888885</v>
       </c>
       <c r="P239" t="n">
         <v>18500</v>
@@ -11415,10 +11415,10 @@
         <v>51</v>
       </c>
       <c r="N257" t="n">
-        <v>4100.45</v>
+        <v>4114.8123467601</v>
       </c>
       <c r="O257" t="n">
-        <v>209122.95</v>
+        <v>209855.4296847651</v>
       </c>
       <c r="P257" t="n">
         <v>26900</v>
@@ -11589,10 +11589,10 @@
         <v>480</v>
       </c>
       <c r="N261" t="n">
-        <v>7969.950169361</v>
+        <v>7988.3991280864</v>
       </c>
       <c r="O261" t="n">
-        <v>3825576.08129328</v>
+        <v>3834431.581481472</v>
       </c>
       <c r="P261" t="n">
         <v>12900</v>
@@ -13317,10 +13317,10 @@
         <v>648</v>
       </c>
       <c r="N299" t="n">
-        <v>22739</v>
+        <v>22855.411262799</v>
       </c>
       <c r="O299" t="n">
-        <v>14734872</v>
+        <v>14810306.49829375</v>
       </c>
       <c r="P299" t="n">
         <v>36900</v>
@@ -13685,10 +13685,10 @@
         <v>60</v>
       </c>
       <c r="N307" t="n">
-        <v>13687</v>
+        <v>13795.340369393</v>
       </c>
       <c r="O307" t="n">
-        <v>821220</v>
+        <v>827720.42216358</v>
       </c>
       <c r="P307" t="n">
         <v>21900</v>
@@ -13869,10 +13869,10 @@
         <v>624</v>
       </c>
       <c r="N311" t="n">
-        <v>8858.16</v>
+        <v>8872.673642818099</v>
       </c>
       <c r="O311" t="n">
-        <v>5527491.84</v>
+        <v>5536548.353118494</v>
       </c>
       <c r="P311" t="n">
         <v>15500</v>
@@ -14736,10 +14736,10 @@
         <v>49</v>
       </c>
       <c r="N330" t="n">
-        <v>20726</v>
+        <v>21127.148387097</v>
       </c>
       <c r="O330" t="n">
-        <v>1015574</v>
+        <v>1035230.270967753</v>
       </c>
       <c r="P330" t="n">
         <v>33900</v>
@@ -14920,10 +14920,10 @@
         <v>1728</v>
       </c>
       <c r="N334" t="n">
-        <v>6849.2</v>
+        <v>6855.7044634378</v>
       </c>
       <c r="O334" t="n">
-        <v>11835417.6</v>
+        <v>11846657.31282052</v>
       </c>
       <c r="P334" t="n">
         <v>11500</v>
@@ -16712,10 +16712,10 @@
         <v>4224</v>
       </c>
       <c r="N373" t="n">
-        <v>1516.0387464358</v>
+        <v>1516.0387455416</v>
       </c>
       <c r="O373" t="n">
-        <v>6403747.664944819</v>
+        <v>6403747.661167718</v>
       </c>
       <c r="P373" t="n">
         <v>2300</v>
@@ -16758,10 +16758,10 @@
         <v>288</v>
       </c>
       <c r="N374" t="n">
-        <v>2458.5126157653</v>
+        <v>2500.9617517986</v>
       </c>
       <c r="O374" t="n">
-        <v>708051.6333404063</v>
+        <v>720276.9845179968</v>
       </c>
       <c r="P374" t="n">
         <v>3500</v>
@@ -16850,10 +16850,10 @@
         <v>288</v>
       </c>
       <c r="N376" t="n">
-        <v>1771.089398827</v>
+        <v>1835.6884042553</v>
       </c>
       <c r="O376" t="n">
-        <v>510073.746862176</v>
+        <v>528678.2604255264</v>
       </c>
       <c r="P376" t="n">
         <v>2500</v>
@@ -16896,10 +16896,10 @@
         <v>720</v>
       </c>
       <c r="N377" t="n">
-        <v>2079.3833258511</v>
+        <v>2079.3833208536</v>
       </c>
       <c r="O377" t="n">
-        <v>1497155.994612792</v>
+        <v>1497155.991014592</v>
       </c>
       <c r="P377" t="n">
         <v>2900</v>
@@ -16942,10 +16942,10 @@
         <v>672</v>
       </c>
       <c r="N378" t="n">
-        <v>1803.0166107644</v>
+        <v>1837.4143839428</v>
       </c>
       <c r="O378" t="n">
-        <v>1211627.162433677</v>
+        <v>1234742.466009562</v>
       </c>
       <c r="P378" t="n">
         <v>2500</v>
@@ -17034,10 +17034,10 @@
         <v>396</v>
       </c>
       <c r="N380" t="n">
-        <v>2056.0822493428</v>
+        <v>2093.8229560229</v>
       </c>
       <c r="O380" t="n">
-        <v>814208.5707397488</v>
+        <v>829153.8905850685</v>
       </c>
       <c r="P380" t="n">
         <v>2900</v>
@@ -17126,10 +17126,10 @@
         <v>864</v>
       </c>
       <c r="N382" t="n">
-        <v>1655.9295385779</v>
+        <v>1751.31108</v>
       </c>
       <c r="O382" t="n">
-        <v>1430723.121331306</v>
+        <v>1513132.77312</v>
       </c>
       <c r="P382" t="n">
         <v>2500</v>
@@ -17641,10 +17641,10 @@
         <v>1440</v>
       </c>
       <c r="N393" t="n">
-        <v>13518</v>
+        <v>13559.454697519</v>
       </c>
       <c r="O393" t="n">
-        <v>19465920</v>
+        <v>19525614.76442736</v>
       </c>
       <c r="P393" t="n">
         <v>21900</v>
@@ -17690,10 +17690,10 @@
         <v>1728</v>
       </c>
       <c r="N394" t="n">
-        <v>9736</v>
+        <v>9760.865567680499</v>
       </c>
       <c r="O394" t="n">
-        <v>16823808</v>
+        <v>16866775.7009519</v>
       </c>
       <c r="P394" t="n">
         <v>15900</v>
@@ -17739,10 +17739,10 @@
         <v>48</v>
       </c>
       <c r="N395" t="n">
-        <v>44470</v>
+        <v>45032.911392405</v>
       </c>
       <c r="O395" t="n">
-        <v>2134560</v>
+        <v>2161579.74683544</v>
       </c>
       <c r="P395" t="n">
         <v>71900</v>
@@ -17788,10 +17788,10 @@
         <v>2160</v>
       </c>
       <c r="N396" t="n">
-        <v>5215</v>
+        <v>5227.7693437806</v>
       </c>
       <c r="O396" t="n">
-        <v>11264400</v>
+        <v>11291981.7825661</v>
       </c>
       <c r="P396" t="n">
         <v>8900</v>
@@ -18394,10 +18394,10 @@
         <v>17</v>
       </c>
       <c r="N409" t="n">
-        <v>2286.1645279383</v>
+        <v>2286.164496124</v>
       </c>
       <c r="O409" t="n">
-        <v>38864.7969749511</v>
+        <v>38864.796434108</v>
       </c>
       <c r="P409" t="n">
         <v>3000</v>
@@ -18750,10 +18750,10 @@
         <v>5844</v>
       </c>
       <c r="N417" t="n">
-        <v>517.2943625967</v>
+        <v>517.29445253004</v>
       </c>
       <c r="O417" t="n">
-        <v>3023068.255015115</v>
+        <v>3023068.780585553</v>
       </c>
       <c r="P417" t="n">
         <v>900</v>
@@ -18882,10 +18882,10 @@
         <v>14791</v>
       </c>
       <c r="N420" t="n">
-        <v>703.79481075491</v>
+        <v>703.79479136392</v>
       </c>
       <c r="O420" t="n">
-        <v>10409829.04587587</v>
+        <v>10409828.75906374</v>
       </c>
       <c r="P420" t="n">
         <v>900</v>
@@ -22373,10 +22373,10 @@
         <v>1</v>
       </c>
       <c r="N499" t="n">
-        <v>4985.4069767442</v>
+        <v>4985.4071856287</v>
       </c>
       <c r="O499" t="n">
-        <v>4985.4069767442</v>
+        <v>4985.4071856287</v>
       </c>
       <c r="P499" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -1155,10 +1155,10 @@
         <v>401</v>
       </c>
       <c r="N19" t="n">
-        <v>4088.8962655602</v>
+        <v>4072</v>
       </c>
       <c r="O19" t="n">
-        <v>1639647.40248964</v>
+        <v>1632872</v>
       </c>
       <c r="P19" t="n">
         <v>7500</v>
@@ -2581,10 +2581,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>15899.011607143</v>
+        <v>15711.964345238</v>
       </c>
       <c r="O55" t="n">
-        <v>763152.557142864</v>
+        <v>754174.2885714241</v>
       </c>
       <c r="P55" t="n">
         <v>28500</v>
@@ -3727,10 +3727,10 @@
         <v>67</v>
       </c>
       <c r="N81" t="n">
-        <v>2644.1214388489</v>
+        <v>2570.16</v>
       </c>
       <c r="O81" t="n">
-        <v>177156.1364028763</v>
+        <v>172200.72</v>
       </c>
       <c r="P81" t="n">
         <v>4700</v>
@@ -3810,10 +3810,10 @@
         <v>72</v>
       </c>
       <c r="N83" t="n">
-        <v>2659.1657943925</v>
+        <v>2563.34</v>
       </c>
       <c r="O83" t="n">
-        <v>191459.93719626</v>
+        <v>184560.48</v>
       </c>
       <c r="P83" t="n">
         <v>4700</v>
@@ -4655,10 +4655,10 @@
         <v>101</v>
       </c>
       <c r="N103" t="n">
-        <v>17263.007447496</v>
+        <v>17207.41</v>
       </c>
       <c r="O103" t="n">
-        <v>1743563.752197096</v>
+        <v>1737948.41</v>
       </c>
       <c r="P103" t="n">
         <v>20000</v>
@@ -5791,10 +5791,10 @@
         <v>24</v>
       </c>
       <c r="N128" t="n">
-        <v>2271.9151051954</v>
+        <v>2267.0481021898</v>
       </c>
       <c r="O128" t="n">
-        <v>54525.9625246896</v>
+        <v>54409.1544525552</v>
       </c>
       <c r="P128" t="n">
         <v>3900</v>
@@ -6147,10 +6147,10 @@
         <v>168</v>
       </c>
       <c r="N136" t="n">
-        <v>3594.2531182796</v>
+        <v>3594.2531034483</v>
       </c>
       <c r="O136" t="n">
-        <v>603834.5238709728</v>
+        <v>603834.5213793144</v>
       </c>
       <c r="P136" t="n">
         <v>6500</v>
@@ -6684,10 +6684,10 @@
         <v>75</v>
       </c>
       <c r="N148" t="n">
-        <v>2718.841814346</v>
+        <v>2696.09</v>
       </c>
       <c r="O148" t="n">
-        <v>203913.13607595</v>
+        <v>202206.75</v>
       </c>
       <c r="P148" t="n">
         <v>8200</v>
@@ -8892,10 +8892,10 @@
         <v>192</v>
       </c>
       <c r="N198" t="n">
-        <v>2701.9479396985</v>
+        <v>2661.82</v>
       </c>
       <c r="O198" t="n">
-        <v>518774.004422112</v>
+        <v>511069.4400000001</v>
       </c>
       <c r="P198" t="n">
         <v>3200</v>
@@ -8974,10 +8974,10 @@
         <v>481</v>
       </c>
       <c r="N200" t="n">
-        <v>2633.2</v>
+        <v>2610</v>
       </c>
       <c r="O200" t="n">
-        <v>1266569.2</v>
+        <v>1255410</v>
       </c>
       <c r="P200" t="n">
         <v>3200</v>
@@ -10468,10 +10468,10 @@
         <v>1</v>
       </c>
       <c r="N235" t="n">
-        <v>30262.214828189</v>
+        <v>30244.600034945</v>
       </c>
       <c r="O235" t="n">
-        <v>30262.214828189</v>
+        <v>30244.600034945</v>
       </c>
       <c r="P235" t="n">
         <v>48900</v>
@@ -11287,10 +11287,10 @@
         <v>34</v>
       </c>
       <c r="N254" t="n">
-        <v>27233.355818182</v>
+        <v>27123.764828283</v>
       </c>
       <c r="O254" t="n">
-        <v>925934.097818188</v>
+        <v>922208.004161622</v>
       </c>
       <c r="P254" t="n">
         <v>44500</v>
@@ -11502,10 +11502,10 @@
         <v>480</v>
       </c>
       <c r="N259" t="n">
-        <v>7988.3991280864</v>
+        <v>7969.9501697531</v>
       </c>
       <c r="O259" t="n">
-        <v>3834431.581481472</v>
+        <v>3825576.081481488</v>
       </c>
       <c r="P259" t="n">
         <v>12900</v>
@@ -11804,10 +11804,10 @@
         <v>562</v>
       </c>
       <c r="N266" t="n">
-        <v>2647.8160651629</v>
+        <v>2634.61</v>
       </c>
       <c r="O266" t="n">
-        <v>1488072.62862155</v>
+        <v>1480650.82</v>
       </c>
       <c r="P266" t="n">
         <v>4200</v>
@@ -11850,10 +11850,10 @@
         <v>487</v>
       </c>
       <c r="N267" t="n">
-        <v>3131.5075106082</v>
+        <v>3113.8900282885</v>
       </c>
       <c r="O267" t="n">
-        <v>1525044.157666193</v>
+        <v>1516464.443776499</v>
       </c>
       <c r="P267" t="n">
         <v>5000</v>
@@ -12034,10 +12034,10 @@
         <v>69</v>
       </c>
       <c r="N271" t="n">
-        <v>4397.0456179775</v>
+        <v>4163.1602247191</v>
       </c>
       <c r="O271" t="n">
-        <v>303396.1476404475</v>
+        <v>287258.0555056179</v>
       </c>
       <c r="P271" t="n">
         <v>6700</v>
@@ -12126,10 +12126,10 @@
         <v>350</v>
       </c>
       <c r="N273" t="n">
-        <v>2510.8902747909</v>
+        <v>2495.98</v>
       </c>
       <c r="O273" t="n">
-        <v>878811.596176815</v>
+        <v>873593</v>
       </c>
       <c r="P273" t="n">
         <v>4100</v>
@@ -12494,10 +12494,10 @@
         <v>277</v>
       </c>
       <c r="N281" t="n">
-        <v>5859.18</v>
+        <v>5791.05</v>
       </c>
       <c r="O281" t="n">
-        <v>1622992.86</v>
+        <v>1604120.85</v>
       </c>
       <c r="P281" t="n">
         <v>9300</v>
@@ -13322,10 +13322,10 @@
         <v>720</v>
       </c>
       <c r="N299" t="n">
-        <v>16092.984749455</v>
+        <v>16058</v>
       </c>
       <c r="O299" t="n">
-        <v>11586949.0196076</v>
+        <v>11561760</v>
       </c>
       <c r="P299" t="n">
         <v>25900</v>
@@ -13368,10 +13368,10 @@
         <v>648</v>
       </c>
       <c r="N300" t="n">
-        <v>25576.890257559</v>
+        <v>25534</v>
       </c>
       <c r="O300" t="n">
-        <v>16573824.88689823</v>
+        <v>16546032</v>
       </c>
       <c r="P300" t="n">
         <v>40900</v>
@@ -13598,10 +13598,10 @@
         <v>60</v>
       </c>
       <c r="N305" t="n">
-        <v>13795.055263158</v>
+        <v>13687</v>
       </c>
       <c r="O305" t="n">
-        <v>827703.31578948</v>
+        <v>821220</v>
       </c>
       <c r="P305" t="n">
         <v>21900</v>
@@ -14194,10 +14194,10 @@
         <v>151</v>
       </c>
       <c r="N318" t="n">
-        <v>32566.857142857</v>
+        <v>32332</v>
       </c>
       <c r="O318" t="n">
-        <v>4917595.428571407</v>
+        <v>4882132</v>
       </c>
       <c r="P318" t="n">
         <v>55900</v>
@@ -14470,10 +14470,10 @@
         <v>168</v>
       </c>
       <c r="N324" t="n">
-        <v>13233.257042254</v>
+        <v>13210</v>
       </c>
       <c r="O324" t="n">
-        <v>2223187.183098672</v>
+        <v>2219280</v>
       </c>
       <c r="P324" t="n">
         <v>23900</v>
@@ -14787,10 +14787,10 @@
         <v>240</v>
       </c>
       <c r="N331" t="n">
-        <v>2657.2435094002</v>
+        <v>2629</v>
       </c>
       <c r="O331" t="n">
-        <v>637738.442256048</v>
+        <v>630960</v>
       </c>
       <c r="P331" t="n">
         <v>4500</v>
@@ -14833,10 +14833,10 @@
         <v>1728</v>
       </c>
       <c r="N332" t="n">
-        <v>6881.8463298379</v>
+        <v>6849.2</v>
       </c>
       <c r="O332" t="n">
-        <v>11891830.45795989</v>
+        <v>11835417.6</v>
       </c>
       <c r="P332" t="n">
         <v>11500</v>
@@ -14971,10 +14971,10 @@
         <v>648</v>
       </c>
       <c r="N335" t="n">
-        <v>6279.1629563669</v>
+        <v>6268</v>
       </c>
       <c r="O335" t="n">
-        <v>4068897.595725751</v>
+        <v>4061664</v>
       </c>
       <c r="P335" t="n">
         <v>10900</v>
@@ -15339,10 +15339,10 @@
         <v>750</v>
       </c>
       <c r="N343" t="n">
-        <v>7639.2713286713</v>
+        <v>7635</v>
       </c>
       <c r="O343" t="n">
-        <v>5729453.496503475</v>
+        <v>5726250</v>
       </c>
       <c r="P343" t="n">
         <v>13900</v>
@@ -16119,10 +16119,10 @@
         <v>2</v>
       </c>
       <c r="N360" t="n">
-        <v>14369.318181818</v>
+        <v>14050</v>
       </c>
       <c r="O360" t="n">
-        <v>28738.636363636</v>
+        <v>28100</v>
       </c>
       <c r="P360" t="n">
         <v>23900</v>
@@ -16165,10 +16165,10 @@
         <v>356</v>
       </c>
       <c r="N361" t="n">
-        <v>8721.3759213759</v>
+        <v>8700</v>
       </c>
       <c r="O361" t="n">
-        <v>3104809.828009821</v>
+        <v>3097200</v>
       </c>
       <c r="P361" t="n">
         <v>14900</v>
@@ -16257,10 +16257,10 @@
         <v>92</v>
       </c>
       <c r="N363" t="n">
-        <v>21884.258426966</v>
+        <v>21762</v>
       </c>
       <c r="O363" t="n">
-        <v>2013351.775280872</v>
+        <v>2002104</v>
       </c>
       <c r="P363" t="n">
         <v>35900</v>
@@ -16303,10 +16303,10 @@
         <v>528</v>
       </c>
       <c r="N364" t="n">
-        <v>3823.6153319644</v>
+        <v>3821</v>
       </c>
       <c r="O364" t="n">
-        <v>2018868.895277203</v>
+        <v>2017488</v>
       </c>
       <c r="P364" t="n">
         <v>5900</v>
@@ -17410,10 +17410,10 @@
         <v>8400</v>
       </c>
       <c r="N388" t="n">
-        <v>1955.7828121686</v>
+        <v>1955.2371130338</v>
       </c>
       <c r="O388" t="n">
-        <v>16428575.62221624</v>
+        <v>16423991.74948392</v>
       </c>
       <c r="P388" t="n">
         <v>3000</v>
@@ -17456,10 +17456,10 @@
         <v>1400</v>
       </c>
       <c r="N389" t="n">
-        <v>1185.8146867168</v>
+        <v>1185.3195655806</v>
       </c>
       <c r="O389" t="n">
-        <v>1660140.56140352</v>
+        <v>1659447.39181284</v>
       </c>
       <c r="P389" t="n">
         <v>1900</v>
@@ -18039,10 +18039,10 @@
         <v>2</v>
       </c>
       <c r="N401" t="n">
-        <v>1537.958258381</v>
+        <v>1530.4499182339</v>
       </c>
       <c r="O401" t="n">
-        <v>3075.916516762</v>
+        <v>3060.8998364678</v>
       </c>
       <c r="P401" t="n">
         <v>2600</v>
@@ -18795,10 +18795,10 @@
         <v>14791</v>
       </c>
       <c r="N418" t="n">
-        <v>703.7947715550901</v>
+        <v>704.67584580877</v>
       </c>
       <c r="O418" t="n">
-        <v>10409828.46607134</v>
+        <v>10422860.43535752</v>
       </c>
       <c r="P418" t="n">
         <v>900</v>
@@ -20200,10 +20200,10 @@
         <v>16</v>
       </c>
       <c r="N449" t="n">
-        <v>7605.4495327103</v>
+        <v>7465.9</v>
       </c>
       <c r="O449" t="n">
-        <v>121687.1925233648</v>
+        <v>119454.4</v>
       </c>
       <c r="P449" t="n">
         <v>11900</v>
@@ -20475,10 +20475,10 @@
         <v>40</v>
       </c>
       <c r="N455" t="n">
-        <v>44654.875337423</v>
+        <v>44113.604171779</v>
       </c>
       <c r="O455" t="n">
-        <v>1786195.01349692</v>
+        <v>1764544.16687116</v>
       </c>
       <c r="P455" t="n">
         <v>71900</v>
@@ -22465,10 +22465,10 @@
         <v>342</v>
       </c>
       <c r="N501" t="n">
-        <v>2655.5149832776</v>
+        <v>2644.9</v>
       </c>
       <c r="O501" t="n">
-        <v>908186.1242809392</v>
+        <v>904555.8</v>
       </c>
       <c r="P501" t="n">
         <v>3900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-18</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-19</t>
         </is>
       </c>
     </row>
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.309157128</v>
+        <v>1811.3091666667</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.64828304</v>
+        <v>326035.650000006</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.7464140994</v>
+        <v>3376.7464051196</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.1250402536</v>
+        <v>823926.1228491823</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.855106383</v>
+        <v>6272.8551336898</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.702978728</v>
+        <v>1354936.708876997</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -2341,10 +2341,10 @@
         <v>65</v>
       </c>
       <c r="N49" t="n">
-        <v>31409.32</v>
+        <v>31566.3666</v>
       </c>
       <c r="O49" t="n">
-        <v>2041605.8</v>
+        <v>2051813.829</v>
       </c>
       <c r="P49" t="n">
         <v>45500</v>
@@ -2500,10 +2500,10 @@
         <v>52</v>
       </c>
       <c r="N53" t="n">
-        <v>16486.407142857</v>
+        <v>16486.406666667</v>
       </c>
       <c r="O53" t="n">
-        <v>857293.1714285639</v>
+        <v>857293.1466666841</v>
       </c>
       <c r="P53" t="n">
         <v>30500</v>
@@ -2581,10 +2581,10 @@
         <v>48</v>
       </c>
       <c r="N55" t="n">
-        <v>15711.964345238</v>
+        <v>15711.964135802</v>
       </c>
       <c r="O55" t="n">
-        <v>754174.2885714241</v>
+        <v>754174.278518496</v>
       </c>
       <c r="P55" t="n">
         <v>28500</v>
@@ -2878,10 +2878,10 @@
         <v>20</v>
       </c>
       <c r="N62" t="n">
-        <v>56906.8085</v>
+        <v>56906.810555556</v>
       </c>
       <c r="O62" t="n">
-        <v>1138136.17</v>
+        <v>1138136.21111112</v>
       </c>
       <c r="P62" t="n">
         <v>95900</v>
@@ -3506,10 +3506,10 @@
         <v>79</v>
       </c>
       <c r="N76" t="n">
-        <v>61666.874241573</v>
+        <v>61666.874364162</v>
       </c>
       <c r="O76" t="n">
-        <v>4871683.065084267</v>
+        <v>4871683.074768798</v>
       </c>
       <c r="P76" t="n">
         <v>98900</v>
@@ -3892,10 +3892,10 @@
         <v>960</v>
       </c>
       <c r="N85" t="n">
-        <v>1950.2139585731</v>
+        <v>1953.5860864553</v>
       </c>
       <c r="O85" t="n">
-        <v>1872205.400230176</v>
+        <v>1875442.642997088</v>
       </c>
       <c r="P85" t="n">
         <v>2900</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.25501002</v>
+        <v>2583.5545646704</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.4108216</v>
+        <v>2790238.929844032</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="J110" t="n">
-        <v>1898</v>
+        <v>1811</v>
       </c>
       <c r="K110" t="n">
         <v>0</v>
@@ -4964,19 +4964,19 @@
         <v>0</v>
       </c>
       <c r="M110" t="n">
-        <v>1898</v>
+        <v>1811</v>
       </c>
       <c r="N110" t="n">
-        <v>5216.8959455416</v>
+        <v>5216.8959284856</v>
       </c>
       <c r="O110" t="n">
-        <v>9901668.504637957</v>
+        <v>9447798.526487421</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
       </c>
       <c r="Q110" t="n">
-        <v>16133000</v>
+        <v>15393500</v>
       </c>
     </row>
     <row r="111">
@@ -5059,10 +5059,10 @@
         <v>6298</v>
       </c>
       <c r="N112" t="n">
-        <v>3158.8608386776</v>
+        <v>3160.7464443118</v>
       </c>
       <c r="O112" t="n">
-        <v>19894505.56199152</v>
+        <v>19906381.10627572</v>
       </c>
       <c r="P112" t="n">
         <v>5600</v>
@@ -5338,10 +5338,10 @@
         <v>144</v>
       </c>
       <c r="N118" t="n">
-        <v>8796</v>
+        <v>8820</v>
       </c>
       <c r="O118" t="n">
-        <v>1266624</v>
+        <v>1270080</v>
       </c>
       <c r="P118" t="n">
         <v>14900</v>
@@ -5471,10 +5471,10 @@
         <v>3024</v>
       </c>
       <c r="N121" t="n">
-        <v>3795.7100076161</v>
+        <v>3795.7100076176</v>
       </c>
       <c r="O121" t="n">
-        <v>11478227.06303109</v>
+        <v>11478227.06303562</v>
       </c>
       <c r="P121" t="n">
         <v>6200</v>
@@ -6147,10 +6147,10 @@
         <v>168</v>
       </c>
       <c r="N136" t="n">
-        <v>3594.2531034483</v>
+        <v>3594.2530785869</v>
       </c>
       <c r="O136" t="n">
-        <v>603834.5213793144</v>
+        <v>603834.5172025992</v>
       </c>
       <c r="P136" t="n">
         <v>6500</v>
@@ -6582,7 +6582,7 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>912</v>
+        <v>864</v>
       </c>
       <c r="K146" t="n">
         <v>0</v>
@@ -6591,19 +6591,19 @@
         <v>0</v>
       </c>
       <c r="M146" t="n">
-        <v>912</v>
+        <v>864</v>
       </c>
       <c r="N146" t="n">
-        <v>12422.462946776</v>
+        <v>12422.462948052</v>
       </c>
       <c r="O146" t="n">
-        <v>11329286.20745971</v>
+        <v>10733007.98711693</v>
       </c>
       <c r="P146" t="n">
         <v>19900</v>
       </c>
       <c r="Q146" t="n">
-        <v>18148800</v>
+        <v>17193600</v>
       </c>
     </row>
     <row r="147">
@@ -6718,7 +6718,7 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>5040</v>
+        <v>4908</v>
       </c>
       <c r="K149" t="n">
         <v>0</v>
@@ -6727,19 +6727,19 @@
         <v>0</v>
       </c>
       <c r="M149" t="n">
-        <v>5040</v>
+        <v>4908</v>
       </c>
       <c r="N149" t="n">
-        <v>3472.2761773616</v>
+        <v>3472.2761978447</v>
       </c>
       <c r="O149" t="n">
-        <v>17500271.93390246</v>
+        <v>17041931.57902179</v>
       </c>
       <c r="P149" t="n">
         <v>5900</v>
       </c>
       <c r="Q149" t="n">
-        <v>29736000</v>
+        <v>28957200</v>
       </c>
     </row>
     <row r="150">
@@ -6823,10 +6823,10 @@
         <v>78</v>
       </c>
       <c r="N151" t="n">
-        <v>3041.6600140449</v>
+        <v>3041.6600141844</v>
       </c>
       <c r="O151" t="n">
-        <v>237249.4810955022</v>
+        <v>237249.4811063832</v>
       </c>
       <c r="P151" t="n">
         <v>5500</v>
@@ -6869,10 +6869,10 @@
         <v>809</v>
       </c>
       <c r="N152" t="n">
-        <v>4371.1712626125</v>
+        <v>4372.0654674395</v>
       </c>
       <c r="O152" t="n">
-        <v>3536277.551453513</v>
+        <v>3537000.963158555</v>
       </c>
       <c r="P152" t="n">
         <v>8900</v>
@@ -7172,10 +7172,10 @@
         <v>10357</v>
       </c>
       <c r="N159" t="n">
-        <v>1532.629025031</v>
+        <v>1534.4227525419</v>
       </c>
       <c r="O159" t="n">
-        <v>15873438.81224607</v>
+        <v>15892016.44807646</v>
       </c>
       <c r="P159" t="n">
         <v>1200</v>
@@ -7611,10 +7611,10 @@
         <v>238</v>
       </c>
       <c r="N169" t="n">
-        <v>3761.6</v>
+        <v>3776.2176165803</v>
       </c>
       <c r="O169" t="n">
-        <v>895260.7999999999</v>
+        <v>898739.7927461114</v>
       </c>
       <c r="P169" t="n">
         <v>6900</v>
@@ -7924,10 +7924,10 @@
         <v>768</v>
       </c>
       <c r="N176" t="n">
-        <v>1630.9244361119</v>
+        <v>1630.924511587</v>
       </c>
       <c r="O176" t="n">
-        <v>1252549.966933939</v>
+        <v>1252550.024898816</v>
       </c>
       <c r="P176" t="n">
         <v>2500</v>
@@ -7970,10 +7970,10 @@
         <v>3744</v>
       </c>
       <c r="N177" t="n">
-        <v>1550.1945724495</v>
+        <v>1550.1946099379</v>
       </c>
       <c r="O177" t="n">
-        <v>5803928.479250927</v>
+        <v>5803928.619607497</v>
       </c>
       <c r="P177" t="n">
         <v>2500</v>
@@ -8016,10 +8016,10 @@
         <v>1248</v>
       </c>
       <c r="N178" t="n">
-        <v>2403.5190521472</v>
+        <v>2403.5197991712</v>
       </c>
       <c r="O178" t="n">
-        <v>2999591.777079706</v>
+        <v>2999592.709365658</v>
       </c>
       <c r="P178" t="n">
         <v>3500</v>
@@ -9138,10 +9138,10 @@
         <v>491</v>
       </c>
       <c r="N204" t="n">
-        <v>1969</v>
+        <v>1974.990872211</v>
       </c>
       <c r="O204" t="n">
-        <v>966779</v>
+        <v>969720.5182556009</v>
       </c>
       <c r="P204" t="n">
         <v>1500</v>
@@ -9220,10 +9220,10 @@
         <v>576</v>
       </c>
       <c r="N206" t="n">
-        <v>8794.48</v>
+        <v>8799.4655328798</v>
       </c>
       <c r="O206" t="n">
-        <v>5065620.48</v>
+        <v>5068492.146938764</v>
       </c>
       <c r="P206" t="n">
         <v>14500</v>
@@ -10004,10 +10004,10 @@
         <v>150</v>
       </c>
       <c r="N224" t="n">
-        <v>4285.1962793572</v>
+        <v>4285.1963341646</v>
       </c>
       <c r="O224" t="n">
-        <v>642779.44190358</v>
+        <v>642779.45012469</v>
       </c>
       <c r="P224" t="n">
         <v>6900</v>
@@ -10514,10 +10514,10 @@
         <v>2160</v>
       </c>
       <c r="N236" t="n">
-        <v>4814.2679265446</v>
+        <v>4814.2679260066</v>
       </c>
       <c r="O236" t="n">
-        <v>10398818.72133634</v>
+        <v>10398818.72017425</v>
       </c>
       <c r="P236" t="n">
         <v>9900</v>
@@ -11241,10 +11241,10 @@
         <v>324</v>
       </c>
       <c r="N253" t="n">
-        <v>22730.48</v>
+        <v>22761.155411606</v>
       </c>
       <c r="O253" t="n">
-        <v>7364675.52</v>
+        <v>7374614.353360344</v>
       </c>
       <c r="P253" t="n">
         <v>36900</v>
@@ -11328,10 +11328,10 @@
         <v>23</v>
       </c>
       <c r="N255" t="n">
-        <v>4100.45</v>
+        <v>4102.8563673709</v>
       </c>
       <c r="O255" t="n">
-        <v>94310.34999999999</v>
+        <v>94365.6964495307</v>
       </c>
       <c r="P255" t="n">
         <v>26900</v>
@@ -13138,10 +13138,10 @@
         <v>1145</v>
       </c>
       <c r="N295" t="n">
-        <v>1778.4728179471</v>
+        <v>1778.4728348758</v>
       </c>
       <c r="O295" t="n">
-        <v>2036351.37654943</v>
+        <v>2036351.395932791</v>
       </c>
       <c r="P295" t="n">
         <v>4900</v>
@@ -13276,10 +13276,10 @@
         <v>1244</v>
       </c>
       <c r="N298" t="n">
-        <v>18016</v>
+        <v>18023.2064</v>
       </c>
       <c r="O298" t="n">
-        <v>22411904</v>
+        <v>22420868.7616</v>
       </c>
       <c r="P298" t="n">
         <v>29900</v>
@@ -13920,10 +13920,10 @@
         <v>28</v>
       </c>
       <c r="N312" t="n">
-        <v>2252.2979910045</v>
+        <v>2252.2981374046</v>
       </c>
       <c r="O312" t="n">
-        <v>63064.343748126</v>
+        <v>63064.3478473288</v>
       </c>
       <c r="P312" t="n">
         <v>3900</v>
@@ -14102,10 +14102,10 @@
         <v>864</v>
       </c>
       <c r="N316" t="n">
-        <v>2328.1186691895</v>
+        <v>2328.1186615921</v>
       </c>
       <c r="O316" t="n">
-        <v>2011494.530179728</v>
+        <v>2011494.523615574</v>
       </c>
       <c r="P316" t="n">
         <v>4500</v>
@@ -15748,10 +15748,10 @@
         <v>355</v>
       </c>
       <c r="N352" t="n">
-        <v>59834</v>
+        <v>60093.865363735</v>
       </c>
       <c r="O352" t="n">
-        <v>21241070</v>
+        <v>21333322.20412593</v>
       </c>
       <c r="P352" t="n">
         <v>7900</v>
@@ -15831,7 +15831,7 @@
         </is>
       </c>
       <c r="J354" t="n">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="K354" t="n">
         <v>0</v>
@@ -15840,19 +15840,19 @@
         <v>0</v>
       </c>
       <c r="M354" t="n">
-        <v>209</v>
+        <v>179</v>
       </c>
       <c r="N354" t="n">
         <v>10755</v>
       </c>
       <c r="O354" t="n">
-        <v>2247795</v>
+        <v>1925145</v>
       </c>
       <c r="P354" t="n">
         <v>17900</v>
       </c>
       <c r="Q354" t="n">
-        <v>3741100</v>
+        <v>3204100</v>
       </c>
     </row>
     <row r="355">
@@ -15981,10 +15981,10 @@
         <v>60</v>
       </c>
       <c r="N357" t="n">
-        <v>40073</v>
+        <v>40318.846625767</v>
       </c>
       <c r="O357" t="n">
-        <v>2404380</v>
+        <v>2419130.79754602</v>
       </c>
       <c r="P357" t="n">
         <v>64900</v>
@@ -16291,7 +16291,7 @@
         </is>
       </c>
       <c r="J364" t="n">
-        <v>528</v>
+        <v>336</v>
       </c>
       <c r="K364" t="n">
         <v>0</v>
@@ -16300,19 +16300,19 @@
         <v>0</v>
       </c>
       <c r="M364" t="n">
-        <v>528</v>
+        <v>336</v>
       </c>
       <c r="N364" t="n">
         <v>3821</v>
       </c>
       <c r="O364" t="n">
-        <v>2017488</v>
+        <v>1283856</v>
       </c>
       <c r="P364" t="n">
         <v>5900</v>
       </c>
       <c r="Q364" t="n">
-        <v>3115200</v>
+        <v>1982400</v>
       </c>
     </row>
     <row r="365">
@@ -16625,10 +16625,10 @@
         <v>4224</v>
       </c>
       <c r="N371" t="n">
-        <v>1516.0387429797</v>
+        <v>1516.0387397625</v>
       </c>
       <c r="O371" t="n">
-        <v>6403747.650346252</v>
+        <v>6403747.6367568</v>
       </c>
       <c r="P371" t="n">
         <v>2300</v>
@@ -16671,10 +16671,10 @@
         <v>288</v>
       </c>
       <c r="N372" t="n">
-        <v>2458.5125152275</v>
+        <v>2463.8091310592</v>
       </c>
       <c r="O372" t="n">
-        <v>708051.60438552</v>
+        <v>709577.0297450495</v>
       </c>
       <c r="P372" t="n">
         <v>3500</v>
@@ -16717,10 +16717,10 @@
         <v>240</v>
       </c>
       <c r="N373" t="n">
-        <v>1907.3924741082</v>
+        <v>1907.3924654378</v>
       </c>
       <c r="O373" t="n">
-        <v>457774.193785968</v>
+        <v>457774.191705072</v>
       </c>
       <c r="P373" t="n">
         <v>2500</v>
@@ -16763,10 +16763,10 @@
         <v>288</v>
       </c>
       <c r="N374" t="n">
-        <v>1771.0893676471</v>
+        <v>1771.0893598234</v>
       </c>
       <c r="O374" t="n">
-        <v>510073.7378823648</v>
+        <v>510073.7356291392</v>
       </c>
       <c r="P374" t="n">
         <v>2500</v>
@@ -16855,10 +16855,10 @@
         <v>672</v>
       </c>
       <c r="N376" t="n">
-        <v>1803.0169240196</v>
+        <v>1803.0169552729</v>
       </c>
       <c r="O376" t="n">
-        <v>1211627.372941171</v>
+        <v>1211627.393943389</v>
       </c>
       <c r="P376" t="n">
         <v>2500</v>
@@ -16947,10 +16947,10 @@
         <v>396</v>
       </c>
       <c r="N378" t="n">
-        <v>2056.0821341463</v>
+        <v>2056.0821161192</v>
       </c>
       <c r="O378" t="n">
-        <v>814208.5251219348</v>
+        <v>814208.5179832031</v>
       </c>
       <c r="P378" t="n">
         <v>2900</v>
@@ -16993,10 +16993,10 @@
         <v>714</v>
       </c>
       <c r="N379" t="n">
-        <v>3224.5697654119</v>
+        <v>3224.5697707424</v>
       </c>
       <c r="O379" t="n">
-        <v>2302342.812504096</v>
+        <v>2302342.816310074</v>
       </c>
       <c r="P379" t="n">
         <v>4500</v>
@@ -17493,7 +17493,7 @@
         </is>
       </c>
       <c r="J390" t="n">
-        <v>2016</v>
+        <v>1948</v>
       </c>
       <c r="K390" t="n">
         <v>0</v>
@@ -17502,19 +17502,19 @@
         <v>0</v>
       </c>
       <c r="M390" t="n">
-        <v>2016</v>
+        <v>1948</v>
       </c>
       <c r="N390" t="n">
         <v>11690</v>
       </c>
       <c r="O390" t="n">
-        <v>23567040</v>
+        <v>22772120</v>
       </c>
       <c r="P390" t="n">
         <v>18900</v>
       </c>
       <c r="Q390" t="n">
-        <v>38102400</v>
+        <v>36817200</v>
       </c>
     </row>
     <row r="391">
@@ -17640,7 +17640,7 @@
         </is>
       </c>
       <c r="J393" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="K393" t="n">
         <v>0</v>
@@ -17649,19 +17649,19 @@
         <v>0</v>
       </c>
       <c r="M393" t="n">
-        <v>48</v>
+        <v>22</v>
       </c>
       <c r="N393" t="n">
         <v>44470</v>
       </c>
       <c r="O393" t="n">
-        <v>2134560</v>
+        <v>978340</v>
       </c>
       <c r="P393" t="n">
         <v>71900</v>
       </c>
       <c r="Q393" t="n">
-        <v>3451200</v>
+        <v>1581800</v>
       </c>
     </row>
     <row r="394">
@@ -17689,7 +17689,7 @@
         </is>
       </c>
       <c r="J394" t="n">
-        <v>2076</v>
+        <v>2010</v>
       </c>
       <c r="K394" t="n">
         <v>0</v>
@@ -17698,19 +17698,19 @@
         <v>0</v>
       </c>
       <c r="M394" t="n">
-        <v>2076</v>
+        <v>2010</v>
       </c>
       <c r="N394" t="n">
         <v>5215</v>
       </c>
       <c r="O394" t="n">
-        <v>10826340</v>
+        <v>10482150</v>
       </c>
       <c r="P394" t="n">
         <v>8900</v>
       </c>
       <c r="Q394" t="n">
-        <v>18476400</v>
+        <v>17889000</v>
       </c>
     </row>
     <row r="395">
@@ -18175,10 +18175,10 @@
         <v>1</v>
       </c>
       <c r="N404" t="n">
-        <v>2357.74</v>
+        <v>2479.6920689655</v>
       </c>
       <c r="O404" t="n">
-        <v>2357.74</v>
+        <v>2479.6920689655</v>
       </c>
       <c r="P404" t="n">
         <v>3000</v>
@@ -18207,7 +18207,7 @@
         </is>
       </c>
       <c r="J405" t="n">
-        <v>554</v>
+        <v>86</v>
       </c>
       <c r="K405" t="n">
         <v>0</v>
@@ -18216,19 +18216,19 @@
         <v>0</v>
       </c>
       <c r="M405" t="n">
-        <v>554</v>
+        <v>86</v>
       </c>
       <c r="N405" t="n">
         <v>1828.64</v>
       </c>
       <c r="O405" t="n">
-        <v>1013066.56</v>
+        <v>157263.04</v>
       </c>
       <c r="P405" t="n">
         <v>2000</v>
       </c>
       <c r="Q405" t="n">
-        <v>1108000</v>
+        <v>172000</v>
       </c>
     </row>
     <row r="406">
@@ -18263,10 +18263,10 @@
         <v>75</v>
       </c>
       <c r="N406" t="n">
-        <v>345.55838633169</v>
+        <v>345.63428985635</v>
       </c>
       <c r="O406" t="n">
-        <v>25916.87897487675</v>
+        <v>25922.57173922625</v>
       </c>
       <c r="P406" t="n">
         <v>600</v>
@@ -18663,10 +18663,10 @@
         <v>5844</v>
       </c>
       <c r="N415" t="n">
-        <v>517.29467353952</v>
+        <v>517.29485088253</v>
       </c>
       <c r="O415" t="n">
-        <v>3023070.072164955</v>
+        <v>3023071.108557506</v>
       </c>
       <c r="P415" t="n">
         <v>900</v>
@@ -18795,10 +18795,10 @@
         <v>14791</v>
       </c>
       <c r="N418" t="n">
-        <v>704.67584580877</v>
+        <v>703.7947515264</v>
       </c>
       <c r="O418" t="n">
-        <v>10422860.43535752</v>
+        <v>10409828.16982698</v>
       </c>
       <c r="P418" t="n">
         <v>900</v>
@@ -19372,10 +19372,10 @@
         <v>569</v>
       </c>
       <c r="N431" t="n">
-        <v>1595.4993541033</v>
+        <v>1595.4991666667</v>
       </c>
       <c r="O431" t="n">
-        <v>907839.1324847777</v>
+        <v>907839.0258333522</v>
       </c>
       <c r="P431" t="n">
         <v>2500</v>
@@ -19467,10 +19467,10 @@
         <v>122</v>
       </c>
       <c r="N433" t="n">
-        <v>6078.9925934066</v>
+        <v>6078.9925962596</v>
       </c>
       <c r="O433" t="n">
-        <v>741637.0963956051</v>
+        <v>741637.0967436712</v>
       </c>
       <c r="P433" t="n">
         <v>18500</v>
@@ -20249,10 +20249,10 @@
         <v>1976</v>
       </c>
       <c r="N450" t="n">
-        <v>7046.9398271765</v>
+        <v>7056.0857581657</v>
       </c>
       <c r="O450" t="n">
-        <v>13924753.09850076</v>
+        <v>13942825.45813542</v>
       </c>
       <c r="P450" t="n">
         <v>9900</v>
@@ -21172,10 +21172,10 @@
         <v>1446</v>
       </c>
       <c r="N471" t="n">
-        <v>2489.1752653486</v>
+        <v>2490.4710359188</v>
       </c>
       <c r="O471" t="n">
-        <v>3599347.433694076</v>
+        <v>3601221.117938585</v>
       </c>
       <c r="P471" t="n">
         <v>3000</v>
@@ -21518,10 +21518,10 @@
         <v>436</v>
       </c>
       <c r="N479" t="n">
-        <v>5497.1753043478</v>
+        <v>5497.1752906977</v>
       </c>
       <c r="O479" t="n">
-        <v>2396768.432695641</v>
+        <v>2396768.426744197</v>
       </c>
       <c r="P479" t="n">
         <v>6500</v>
@@ -21603,10 +21603,10 @@
         <v>5129</v>
       </c>
       <c r="N481" t="n">
-        <v>1794.2879648314</v>
+        <v>1796.1048285838</v>
       </c>
       <c r="O481" t="n">
-        <v>9202902.97162025</v>
+        <v>9212221.66580631</v>
       </c>
       <c r="P481" t="n">
         <v>1600</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -2341,10 +2341,10 @@
         <v>65</v>
       </c>
       <c r="N49" t="n">
-        <v>31566.3666</v>
+        <v>31409.32</v>
       </c>
       <c r="O49" t="n">
-        <v>2051813.829</v>
+        <v>2041605.8</v>
       </c>
       <c r="P49" t="n">
         <v>45500</v>
@@ -3892,10 +3892,10 @@
         <v>960</v>
       </c>
       <c r="N85" t="n">
-        <v>1953.5860864553</v>
+        <v>1950.2139481268</v>
       </c>
       <c r="O85" t="n">
-        <v>1875442.642997088</v>
+        <v>1872205.390201728</v>
       </c>
       <c r="P85" t="n">
         <v>2900</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2583.5545646704</v>
+        <v>2582.2549874182</v>
       </c>
       <c r="O108" t="n">
-        <v>2790238.929844032</v>
+        <v>2788835.386411656</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -5059,10 +5059,10 @@
         <v>6298</v>
       </c>
       <c r="N112" t="n">
-        <v>3160.7464443118</v>
+        <v>3158.8608391782</v>
       </c>
       <c r="O112" t="n">
-        <v>19906381.10627572</v>
+        <v>19894505.5651443</v>
       </c>
       <c r="P112" t="n">
         <v>5600</v>
@@ -5338,10 +5338,10 @@
         <v>144</v>
       </c>
       <c r="N118" t="n">
-        <v>8820</v>
+        <v>8796</v>
       </c>
       <c r="O118" t="n">
-        <v>1270080</v>
+        <v>1266624</v>
       </c>
       <c r="P118" t="n">
         <v>14900</v>
@@ -6869,10 +6869,10 @@
         <v>809</v>
       </c>
       <c r="N152" t="n">
-        <v>4372.0654674395</v>
+        <v>4371.1712628708</v>
       </c>
       <c r="O152" t="n">
-        <v>3537000.963158555</v>
+        <v>3536277.551662477</v>
       </c>
       <c r="P152" t="n">
         <v>8900</v>
@@ -7172,10 +7172,10 @@
         <v>10357</v>
       </c>
       <c r="N159" t="n">
-        <v>1534.4227525419</v>
+        <v>1532.6290227489</v>
       </c>
       <c r="O159" t="n">
-        <v>15892016.44807646</v>
+        <v>15873438.78861036</v>
       </c>
       <c r="P159" t="n">
         <v>1200</v>
@@ -7611,10 +7611,10 @@
         <v>238</v>
       </c>
       <c r="N169" t="n">
-        <v>3776.2176165803</v>
+        <v>3761.6</v>
       </c>
       <c r="O169" t="n">
-        <v>898739.7927461114</v>
+        <v>895260.7999999999</v>
       </c>
       <c r="P169" t="n">
         <v>6900</v>
@@ -9138,10 +9138,10 @@
         <v>491</v>
       </c>
       <c r="N204" t="n">
-        <v>1974.990872211</v>
+        <v>1969</v>
       </c>
       <c r="O204" t="n">
-        <v>969720.5182556009</v>
+        <v>966779</v>
       </c>
       <c r="P204" t="n">
         <v>1500</v>
@@ -9220,10 +9220,10 @@
         <v>576</v>
       </c>
       <c r="N206" t="n">
-        <v>8799.4655328798</v>
+        <v>8794.48</v>
       </c>
       <c r="O206" t="n">
-        <v>5068492.146938764</v>
+        <v>5065620.48</v>
       </c>
       <c r="P206" t="n">
         <v>14500</v>
@@ -11241,10 +11241,10 @@
         <v>324</v>
       </c>
       <c r="N253" t="n">
-        <v>22761.155411606</v>
+        <v>22730.48</v>
       </c>
       <c r="O253" t="n">
-        <v>7374614.353360344</v>
+        <v>7364675.52</v>
       </c>
       <c r="P253" t="n">
         <v>36900</v>
@@ -11328,10 +11328,10 @@
         <v>23</v>
       </c>
       <c r="N255" t="n">
-        <v>4102.8563673709</v>
+        <v>4100.45</v>
       </c>
       <c r="O255" t="n">
-        <v>94365.6964495307</v>
+        <v>94310.34999999999</v>
       </c>
       <c r="P255" t="n">
         <v>26900</v>
@@ -13276,10 +13276,10 @@
         <v>1244</v>
       </c>
       <c r="N298" t="n">
-        <v>18023.2064</v>
+        <v>18016</v>
       </c>
       <c r="O298" t="n">
-        <v>22420868.7616</v>
+        <v>22411904</v>
       </c>
       <c r="P298" t="n">
         <v>29900</v>
@@ -15748,10 +15748,10 @@
         <v>355</v>
       </c>
       <c r="N352" t="n">
-        <v>60093.865363735</v>
+        <v>59834</v>
       </c>
       <c r="O352" t="n">
-        <v>21333322.20412593</v>
+        <v>21241070</v>
       </c>
       <c r="P352" t="n">
         <v>7900</v>
@@ -15981,10 +15981,10 @@
         <v>60</v>
       </c>
       <c r="N357" t="n">
-        <v>40318.846625767</v>
+        <v>40073</v>
       </c>
       <c r="O357" t="n">
-        <v>2419130.79754602</v>
+        <v>2404380</v>
       </c>
       <c r="P357" t="n">
         <v>64900</v>
@@ -16671,10 +16671,10 @@
         <v>288</v>
       </c>
       <c r="N372" t="n">
-        <v>2463.8091310592</v>
+        <v>2458.5124991023</v>
       </c>
       <c r="O372" t="n">
-        <v>709577.0297450495</v>
+        <v>708051.5997414624</v>
       </c>
       <c r="P372" t="n">
         <v>3500</v>
@@ -18175,10 +18175,10 @@
         <v>1</v>
       </c>
       <c r="N404" t="n">
-        <v>2479.6920689655</v>
+        <v>2357.74</v>
       </c>
       <c r="O404" t="n">
-        <v>2479.6920689655</v>
+        <v>2357.74</v>
       </c>
       <c r="P404" t="n">
         <v>3000</v>
@@ -18263,10 +18263,10 @@
         <v>75</v>
       </c>
       <c r="N406" t="n">
-        <v>345.63428985635</v>
+        <v>345.55838597724</v>
       </c>
       <c r="O406" t="n">
-        <v>25922.57173922625</v>
+        <v>25916.878948293</v>
       </c>
       <c r="P406" t="n">
         <v>600</v>
@@ -20249,10 +20249,10 @@
         <v>1976</v>
       </c>
       <c r="N450" t="n">
-        <v>7056.0857581657</v>
+        <v>7046.9398269522</v>
       </c>
       <c r="O450" t="n">
-        <v>13942825.45813542</v>
+        <v>13924753.09805755</v>
       </c>
       <c r="P450" t="n">
         <v>9900</v>
@@ -21172,10 +21172,10 @@
         <v>1446</v>
       </c>
       <c r="N471" t="n">
-        <v>2490.4710359188</v>
+        <v>2489.1752628839</v>
       </c>
       <c r="O471" t="n">
-        <v>3601221.117938585</v>
+        <v>3599347.430130119</v>
       </c>
       <c r="P471" t="n">
         <v>3000</v>
@@ -21603,10 +21603,10 @@
         <v>5129</v>
       </c>
       <c r="N481" t="n">
-        <v>1796.1048285838</v>
+        <v>1794.2879574714</v>
       </c>
       <c r="O481" t="n">
-        <v>9212221.66580631</v>
+        <v>9202902.933870811</v>
       </c>
       <c r="P481" t="n">
         <v>1600</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-20</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3093916756</v>
+        <v>1830.8488673139</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.690501608</v>
+        <v>329552.796116502</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8551705566</v>
+        <v>6272.8551798561</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.716840226</v>
+        <v>1354936.718848918</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -4875,10 +4875,10 @@
         <v>1080</v>
       </c>
       <c r="N108" t="n">
-        <v>2582.2549620637</v>
+        <v>2582.2549607893</v>
       </c>
       <c r="O108" t="n">
-        <v>2788835.359028796</v>
+        <v>2788835.357652444</v>
       </c>
       <c r="P108" t="n">
         <v>4500</v>
@@ -4967,10 +4967,10 @@
         <v>1811</v>
       </c>
       <c r="N110" t="n">
-        <v>5216.8958877086</v>
+        <v>5216.8958858357</v>
       </c>
       <c r="O110" t="n">
-        <v>9447798.452640275</v>
+        <v>9447798.449248454</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
@@ -5059,10 +5059,10 @@
         <v>6298</v>
       </c>
       <c r="N112" t="n">
-        <v>3158.8608391782</v>
+        <v>3158.86083922</v>
       </c>
       <c r="O112" t="n">
-        <v>19894505.5651443</v>
+        <v>19894505.56540756</v>
       </c>
       <c r="P112" t="n">
         <v>5600</v>
@@ -5471,10 +5471,10 @@
         <v>3024</v>
       </c>
       <c r="N121" t="n">
-        <v>3795.7100076176</v>
+        <v>3795.7100076234</v>
       </c>
       <c r="O121" t="n">
-        <v>11478227.06303562</v>
+        <v>11478227.06305316</v>
       </c>
       <c r="P121" t="n">
         <v>6200</v>
@@ -5745,10 +5745,10 @@
         <v>24</v>
       </c>
       <c r="N127" t="n">
-        <v>2267.0480923608</v>
+        <v>2267.0480857514</v>
       </c>
       <c r="O127" t="n">
-        <v>54409.1542166592</v>
+        <v>54409.1540580336</v>
       </c>
       <c r="P127" t="n">
         <v>3900</v>
@@ -6101,10 +6101,10 @@
         <v>168</v>
       </c>
       <c r="N135" t="n">
-        <v>3594.2530181818</v>
+        <v>3594.2529978118</v>
       </c>
       <c r="O135" t="n">
-        <v>603834.5070545424</v>
+        <v>603834.5036323824</v>
       </c>
       <c r="P135" t="n">
         <v>6500</v>
@@ -6684,10 +6684,10 @@
         <v>4908</v>
       </c>
       <c r="N148" t="n">
-        <v>3472.2762167406</v>
+        <v>3472.276224504</v>
       </c>
       <c r="O148" t="n">
-        <v>17041931.67176287</v>
+        <v>17041931.70986563</v>
       </c>
       <c r="P148" t="n">
         <v>5900</v>
@@ -6777,10 +6777,10 @@
         <v>78</v>
       </c>
       <c r="N150" t="n">
-        <v>3041.6600141844</v>
+        <v>3041.6600141945</v>
       </c>
       <c r="O150" t="n">
-        <v>237249.4811063832</v>
+        <v>237249.481107171</v>
       </c>
       <c r="P150" t="n">
         <v>5500</v>
@@ -6823,10 +6823,10 @@
         <v>809</v>
       </c>
       <c r="N151" t="n">
-        <v>4371.1712629569</v>
+        <v>4371.7675214841</v>
       </c>
       <c r="O151" t="n">
-        <v>3536277.551732132</v>
+        <v>3536759.924880637</v>
       </c>
       <c r="P151" t="n">
         <v>8900</v>
@@ -6992,10 +6992,10 @@
         <v>2487</v>
       </c>
       <c r="N155" t="n">
-        <v>3655.96</v>
+        <v>3668.2806919793</v>
       </c>
       <c r="O155" t="n">
-        <v>9092372.52</v>
+        <v>9123014.08095252</v>
       </c>
       <c r="P155" t="n">
         <v>5500</v>
@@ -7041,10 +7041,10 @@
         <v>5436</v>
       </c>
       <c r="N156" t="n">
-        <v>4648.6</v>
+        <v>4649.4131187686</v>
       </c>
       <c r="O156" t="n">
-        <v>25269789.6</v>
+        <v>25274209.71362611</v>
       </c>
       <c r="P156" t="n">
         <v>8900</v>
@@ -7878,10 +7878,10 @@
         <v>768</v>
       </c>
       <c r="N175" t="n">
-        <v>1630.9246047904</v>
+        <v>1630.9246075494</v>
       </c>
       <c r="O175" t="n">
-        <v>1252550.096479027</v>
+        <v>1252550.098597939</v>
       </c>
       <c r="P175" t="n">
         <v>2500</v>
@@ -7924,10 +7924,10 @@
         <v>3744</v>
       </c>
       <c r="N176" t="n">
-        <v>1550.1946673374</v>
+        <v>1551.3666948085</v>
       </c>
       <c r="O176" t="n">
-        <v>5803928.834511226</v>
+        <v>5808316.905363023</v>
       </c>
       <c r="P176" t="n">
         <v>2500</v>
@@ -7970,10 +7970,10 @@
         <v>1248</v>
       </c>
       <c r="N177" t="n">
-        <v>2403.5202775057</v>
+        <v>2407.4618268285</v>
       </c>
       <c r="O177" t="n">
-        <v>2999593.306327114</v>
+        <v>3004512.359881968</v>
       </c>
       <c r="P177" t="n">
         <v>3500</v>
@@ -8846,10 +8846,10 @@
         <v>192</v>
       </c>
       <c r="N197" t="n">
-        <v>2661.82</v>
+        <v>2668.524836272</v>
       </c>
       <c r="O197" t="n">
-        <v>511069.4400000001</v>
+        <v>512356.768564224</v>
       </c>
       <c r="P197" t="n">
         <v>3200</v>
@@ -8928,10 +8928,10 @@
         <v>481</v>
       </c>
       <c r="N199" t="n">
-        <v>2610</v>
+        <v>2613.8724035608</v>
       </c>
       <c r="O199" t="n">
-        <v>1255410</v>
+        <v>1257272.626112745</v>
       </c>
       <c r="P199" t="n">
         <v>3200</v>
@@ -8969,10 +8969,10 @@
         <v>191</v>
       </c>
       <c r="N200" t="n">
-        <v>2081</v>
+        <v>2086.0024038462</v>
       </c>
       <c r="O200" t="n">
-        <v>397471</v>
+        <v>398426.4591346242</v>
       </c>
       <c r="P200" t="n">
         <v>3200</v>
@@ -9392,10 +9392,10 @@
         <v>249</v>
       </c>
       <c r="N210" t="n">
-        <v>24538.02</v>
+        <v>25442.647465438</v>
       </c>
       <c r="O210" t="n">
-        <v>6109966.98</v>
+        <v>6335219.218894062</v>
       </c>
       <c r="P210" t="n">
         <v>52900</v>
@@ -9958,10 +9958,10 @@
         <v>150</v>
       </c>
       <c r="N223" t="n">
-        <v>4285.1963420724</v>
+        <v>4285.1963819095</v>
       </c>
       <c r="O223" t="n">
-        <v>642779.45131086</v>
+        <v>642779.4572864249</v>
       </c>
       <c r="P223" t="n">
         <v>6900</v>
@@ -11282,10 +11282,10 @@
         <v>23</v>
       </c>
       <c r="N254" t="n">
-        <v>4100.45</v>
+        <v>4107.6818342152</v>
       </c>
       <c r="O254" t="n">
-        <v>94310.34999999999</v>
+        <v>94476.68218694961</v>
       </c>
       <c r="P254" t="n">
         <v>26900</v>
@@ -11456,10 +11456,10 @@
         <v>480</v>
       </c>
       <c r="N258" t="n">
-        <v>7969.9501704105</v>
+        <v>7969.9501706749</v>
       </c>
       <c r="O258" t="n">
-        <v>3825576.08179704</v>
+        <v>3825576.081923952</v>
       </c>
       <c r="P258" t="n">
         <v>12900</v>
@@ -13092,10 +13092,10 @@
         <v>1145</v>
       </c>
       <c r="N294" t="n">
-        <v>1778.4728413344</v>
+        <v>1778.4728487518</v>
       </c>
       <c r="O294" t="n">
-        <v>2036351.403327888</v>
+        <v>2036351.411820811</v>
       </c>
       <c r="P294" t="n">
         <v>4900</v>
@@ -13874,10 +13874,10 @@
         <v>28</v>
       </c>
       <c r="N311" t="n">
-        <v>2252.298328125</v>
+        <v>2252.2983673469</v>
       </c>
       <c r="O311" t="n">
-        <v>63064.3531875</v>
+        <v>63064.3542857132</v>
       </c>
       <c r="P311" t="n">
         <v>3900</v>
@@ -15063,10 +15063,10 @@
         <v>2016</v>
       </c>
       <c r="N337" t="n">
-        <v>6645</v>
+        <v>6648.7102177554</v>
       </c>
       <c r="O337" t="n">
-        <v>13396320</v>
+        <v>13403799.79899489</v>
       </c>
       <c r="P337" t="n">
         <v>10900</v>
@@ -15201,10 +15201,10 @@
         <v>480</v>
       </c>
       <c r="N340" t="n">
-        <v>3898</v>
+        <v>3904.464344942</v>
       </c>
       <c r="O340" t="n">
-        <v>1871040</v>
+        <v>1874142.88557216</v>
       </c>
       <c r="P340" t="n">
         <v>6900</v>
@@ -16625,10 +16625,10 @@
         <v>288</v>
       </c>
       <c r="N371" t="n">
-        <v>2458.5124311594</v>
+        <v>2458.5124201742</v>
       </c>
       <c r="O371" t="n">
-        <v>708051.5801739072</v>
+        <v>708051.5770101696</v>
       </c>
       <c r="P371" t="n">
         <v>3500</v>
@@ -16717,10 +16717,10 @@
         <v>288</v>
       </c>
       <c r="N373" t="n">
-        <v>1771.0893441415</v>
+        <v>1771.0893205318</v>
       </c>
       <c r="O373" t="n">
-        <v>510073.731112752</v>
+        <v>510073.7243131584</v>
       </c>
       <c r="P373" t="n">
         <v>2500</v>
@@ -16809,10 +16809,10 @@
         <v>672</v>
       </c>
       <c r="N375" t="n">
-        <v>1803.0169781803</v>
+        <v>1803.0169868096</v>
       </c>
       <c r="O375" t="n">
-        <v>1211627.409337162</v>
+        <v>1211627.415136051</v>
       </c>
       <c r="P375" t="n">
         <v>2500</v>
@@ -17993,10 +17993,10 @@
         <v>2</v>
       </c>
       <c r="N400" t="n">
-        <v>1530.4499180664</v>
+        <v>1538.0108069164</v>
       </c>
       <c r="O400" t="n">
-        <v>3060.8998361328</v>
+        <v>3076.0216138328</v>
       </c>
       <c r="P400" t="n">
         <v>2600</v>
@@ -18617,10 +18617,10 @@
         <v>5844</v>
       </c>
       <c r="N414" t="n">
-        <v>517.2950312417501</v>
+        <v>517.29511103247</v>
       </c>
       <c r="O414" t="n">
-        <v>3023072.162576787</v>
+        <v>3023072.628873755</v>
       </c>
       <c r="P414" t="n">
         <v>900</v>
@@ -18749,10 +18749,10 @@
         <v>14791</v>
       </c>
       <c r="N417" t="n">
-        <v>703.7947376286299</v>
+        <v>703.79473431536</v>
       </c>
       <c r="O417" t="n">
-        <v>10409827.96426507</v>
+        <v>10409827.91525849</v>
       </c>
       <c r="P417" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-21</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1830.8488673139</v>
+        <v>1811.3101499423</v>
       </c>
       <c r="O13" t="n">
-        <v>329552.796116502</v>
+        <v>326035.826989614</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -3061,10 +3061,10 @@
         <v>25</v>
       </c>
       <c r="N66" t="n">
-        <v>200072.20240385</v>
+        <v>200072.2037234</v>
       </c>
       <c r="O66" t="n">
-        <v>5001805.06009625</v>
+        <v>5001805.093084999</v>
       </c>
       <c r="P66" t="n">
         <v>312000</v>
@@ -3103,10 +3103,10 @@
         <v>2</v>
       </c>
       <c r="N67" t="n">
-        <v>174389.85125</v>
+        <v>174389.9</v>
       </c>
       <c r="O67" t="n">
-        <v>348779.7025</v>
+        <v>348779.8</v>
       </c>
       <c r="P67" t="n">
         <v>368200</v>
@@ -3150,10 +3150,10 @@
         <v>16</v>
       </c>
       <c r="N68" t="n">
-        <v>251809.29230769</v>
+        <v>251809.29090909</v>
       </c>
       <c r="O68" t="n">
-        <v>4028948.67692304</v>
+        <v>4028948.65454544</v>
       </c>
       <c r="P68" t="n">
         <v>584000</v>
@@ -3197,10 +3197,10 @@
         <v>15</v>
       </c>
       <c r="N69" t="n">
-        <v>344599.17844444</v>
+        <v>344599.17815789</v>
       </c>
       <c r="O69" t="n">
-        <v>5168987.676666601</v>
+        <v>5168987.67236835</v>
       </c>
       <c r="P69" t="n">
         <v>532900</v>
@@ -3892,10 +3892,10 @@
         <v>960</v>
       </c>
       <c r="N85" t="n">
-        <v>1950.2139095128</v>
+        <v>1950.2137350835</v>
       </c>
       <c r="O85" t="n">
-        <v>1872205.353132288</v>
+        <v>1872205.18568016</v>
       </c>
       <c r="P85" t="n">
         <v>2900</v>
@@ -4967,10 +4967,10 @@
         <v>1811</v>
       </c>
       <c r="N110" t="n">
-        <v>5216.8958858357</v>
+        <v>5216.8958827104</v>
       </c>
       <c r="O110" t="n">
-        <v>9447798.449248454</v>
+        <v>9447798.443588534</v>
       </c>
       <c r="P110" t="n">
         <v>8500</v>
@@ -5059,10 +5059,10 @@
         <v>6298</v>
       </c>
       <c r="N112" t="n">
-        <v>3158.86083922</v>
+        <v>3158.8608398885</v>
       </c>
       <c r="O112" t="n">
-        <v>19894505.56540756</v>
+        <v>19894505.56961777</v>
       </c>
       <c r="P112" t="n">
         <v>5600</v>
@@ -5197,10 +5197,10 @@
         <v>224</v>
       </c>
       <c r="N115" t="n">
-        <v>2694.8230922931</v>
+        <v>2694.8230326296</v>
       </c>
       <c r="O115" t="n">
-        <v>603640.3726736545</v>
+        <v>603640.3593090305</v>
       </c>
       <c r="P115" t="n">
         <v>4900</v>
@@ -5471,10 +5471,10 @@
         <v>3024</v>
       </c>
       <c r="N121" t="n">
-        <v>3795.7100076234</v>
+        <v>3795.7100076292</v>
       </c>
       <c r="O121" t="n">
-        <v>11478227.06305316</v>
+        <v>11478227.0630707</v>
       </c>
       <c r="P121" t="n">
         <v>6200</v>
@@ -6101,10 +6101,10 @@
         <v>168</v>
       </c>
       <c r="N135" t="n">
-        <v>3594.2529978118</v>
+        <v>3594.2529721816</v>
       </c>
       <c r="O135" t="n">
-        <v>603834.5036323824</v>
+        <v>603834.4993265088</v>
       </c>
       <c r="P135" t="n">
         <v>6500</v>
@@ -6684,10 +6684,10 @@
         <v>4908</v>
       </c>
       <c r="N148" t="n">
-        <v>3472.276224504</v>
+        <v>3472.2762270961</v>
       </c>
       <c r="O148" t="n">
-        <v>17041931.70986563</v>
+        <v>17041931.72258766</v>
       </c>
       <c r="P148" t="n">
         <v>5900</v>
@@ -6777,10 +6777,10 @@
         <v>78</v>
       </c>
       <c r="N150" t="n">
-        <v>3041.6600141945</v>
+        <v>3041.6600142959</v>
       </c>
       <c r="O150" t="n">
-        <v>237249.481107171</v>
+        <v>237249.4811150802</v>
       </c>
       <c r="P150" t="n">
         <v>5500</v>
@@ -6823,10 +6823,10 @@
         <v>809</v>
       </c>
       <c r="N151" t="n">
-        <v>4371.7675214841</v>
+        <v>4371.1712631292</v>
       </c>
       <c r="O151" t="n">
-        <v>3536759.924880637</v>
+        <v>3536277.551871523</v>
       </c>
       <c r="P151" t="n">
         <v>8900</v>
@@ -6992,10 +6992,10 @@
         <v>2487</v>
       </c>
       <c r="N155" t="n">
-        <v>3668.2806919793</v>
+        <v>3655.96</v>
       </c>
       <c r="O155" t="n">
-        <v>9123014.08095252</v>
+        <v>9092372.52</v>
       </c>
       <c r="P155" t="n">
         <v>5500</v>
@@ -7041,10 +7041,10 @@
         <v>5436</v>
       </c>
       <c r="N156" t="n">
-        <v>4649.4131187686</v>
+        <v>4648.6</v>
       </c>
       <c r="O156" t="n">
-        <v>25274209.71362611</v>
+        <v>25269789.6</v>
       </c>
       <c r="P156" t="n">
         <v>8900</v>
@@ -7878,10 +7878,10 @@
         <v>768</v>
       </c>
       <c r="N175" t="n">
-        <v>1630.9246075494</v>
+        <v>1630.9246283479</v>
       </c>
       <c r="O175" t="n">
-        <v>1252550.098597939</v>
+        <v>1252550.114571187</v>
       </c>
       <c r="P175" t="n">
         <v>2500</v>
@@ -7924,10 +7924,10 @@
         <v>3744</v>
       </c>
       <c r="N176" t="n">
-        <v>1551.3666948085</v>
+        <v>1550.1947087933</v>
       </c>
       <c r="O176" t="n">
-        <v>5808316.905363023</v>
+        <v>5803928.989722115</v>
       </c>
       <c r="P176" t="n">
         <v>2500</v>
@@ -7970,10 +7970,10 @@
         <v>1248</v>
       </c>
       <c r="N177" t="n">
-        <v>2407.4618268285</v>
+        <v>2403.5207171448</v>
       </c>
       <c r="O177" t="n">
-        <v>3004512.359881968</v>
+        <v>2999593.854996711</v>
       </c>
       <c r="P177" t="n">
         <v>3500</v>
@@ -8805,10 +8805,10 @@
         <v>1415</v>
       </c>
       <c r="N196" t="n">
-        <v>4196.872541806</v>
+        <v>4196.8725453531</v>
       </c>
       <c r="O196" t="n">
-        <v>5938574.646655491</v>
+        <v>5938574.651674636</v>
       </c>
       <c r="P196" t="n">
         <v>5900</v>
@@ -8846,10 +8846,10 @@
         <v>192</v>
       </c>
       <c r="N197" t="n">
-        <v>2668.524836272</v>
+        <v>2661.82</v>
       </c>
       <c r="O197" t="n">
-        <v>512356.768564224</v>
+        <v>511069.4400000001</v>
       </c>
       <c r="P197" t="n">
         <v>3200</v>
@@ -8928,10 +8928,10 @@
         <v>481</v>
       </c>
       <c r="N199" t="n">
-        <v>2613.8724035608</v>
+        <v>2610</v>
       </c>
       <c r="O199" t="n">
-        <v>1257272.626112745</v>
+        <v>1255410</v>
       </c>
       <c r="P199" t="n">
         <v>3200</v>
@@ -8969,10 +8969,10 @@
         <v>191</v>
       </c>
       <c r="N200" t="n">
-        <v>2086.0024038462</v>
+        <v>2081</v>
       </c>
       <c r="O200" t="n">
-        <v>398426.4591346242</v>
+        <v>397471</v>
       </c>
       <c r="P200" t="n">
         <v>3200</v>
@@ -9392,10 +9392,10 @@
         <v>249</v>
       </c>
       <c r="N210" t="n">
-        <v>25442.647465438</v>
+        <v>24538.02</v>
       </c>
       <c r="O210" t="n">
-        <v>6335219.218894062</v>
+        <v>6109966.98</v>
       </c>
       <c r="P210" t="n">
         <v>52900</v>
@@ -9958,10 +9958,10 @@
         <v>150</v>
       </c>
       <c r="N223" t="n">
-        <v>4285.1963819095</v>
+        <v>4285.1964141414</v>
       </c>
       <c r="O223" t="n">
-        <v>642779.4572864249</v>
+        <v>642779.4621212101</v>
       </c>
       <c r="P223" t="n">
         <v>6900</v>
@@ -11282,10 +11282,10 @@
         <v>23</v>
       </c>
       <c r="N254" t="n">
-        <v>4107.6818342152</v>
+        <v>4100.45</v>
       </c>
       <c r="O254" t="n">
-        <v>94476.68218694961</v>
+        <v>94310.34999999999</v>
       </c>
       <c r="P254" t="n">
         <v>26900</v>
@@ -11456,10 +11456,10 @@
         <v>480</v>
       </c>
       <c r="N258" t="n">
-        <v>7969.9501706749</v>
+        <v>7969.9501710731</v>
       </c>
       <c r="O258" t="n">
-        <v>3825576.081923952</v>
+        <v>3825576.082115088</v>
       </c>
       <c r="P258" t="n">
         <v>12900</v>
@@ -13092,10 +13092,10 @@
         <v>1145</v>
       </c>
       <c r="N294" t="n">
-        <v>1778.4728487518</v>
+        <v>1778.4728562081</v>
       </c>
       <c r="O294" t="n">
-        <v>2036351.411820811</v>
+        <v>2036351.420358275</v>
       </c>
       <c r="P294" t="n">
         <v>4900</v>
@@ -14056,10 +14056,10 @@
         <v>864</v>
       </c>
       <c r="N315" t="n">
-        <v>2328.118659892</v>
+        <v>2328.1186586141</v>
       </c>
       <c r="O315" t="n">
-        <v>2011494.522146688</v>
+        <v>2011494.521042582</v>
       </c>
       <c r="P315" t="n">
         <v>4500</v>
@@ -15063,10 +15063,10 @@
         <v>2016</v>
       </c>
       <c r="N337" t="n">
-        <v>6648.7102177554</v>
+        <v>6645</v>
       </c>
       <c r="O337" t="n">
-        <v>13403799.79899489</v>
+        <v>13396320</v>
       </c>
       <c r="P337" t="n">
         <v>10900</v>
@@ -15201,10 +15201,10 @@
         <v>480</v>
       </c>
       <c r="N340" t="n">
-        <v>3904.464344942</v>
+        <v>3898</v>
       </c>
       <c r="O340" t="n">
-        <v>1874142.88557216</v>
+        <v>1871040</v>
       </c>
       <c r="P340" t="n">
         <v>6900</v>
@@ -16579,10 +16579,10 @@
         <v>4224</v>
       </c>
       <c r="N370" t="n">
-        <v>1516.0387386003</v>
+        <v>1516.0387367881</v>
       </c>
       <c r="O370" t="n">
-        <v>6403747.631847667</v>
+        <v>6403747.624192934</v>
       </c>
       <c r="P370" t="n">
         <v>2300</v>
@@ -16625,10 +16625,10 @@
         <v>288</v>
       </c>
       <c r="N371" t="n">
-        <v>2458.5124201742</v>
+        <v>2458.5124119143</v>
       </c>
       <c r="O371" t="n">
-        <v>708051.5770101696</v>
+        <v>708051.5746313184</v>
       </c>
       <c r="P371" t="n">
         <v>3500</v>
@@ -16763,10 +16763,10 @@
         <v>720</v>
       </c>
       <c r="N374" t="n">
-        <v>2079.3832881866</v>
+        <v>2079.3832679245</v>
       </c>
       <c r="O374" t="n">
-        <v>1497155.967494352</v>
+        <v>1497155.95290564</v>
       </c>
       <c r="P374" t="n">
         <v>2900</v>
@@ -16809,10 +16809,10 @@
         <v>672</v>
       </c>
       <c r="N375" t="n">
-        <v>1803.0169868096</v>
+        <v>1803.0170831592</v>
       </c>
       <c r="O375" t="n">
-        <v>1211627.415136051</v>
+        <v>1211627.479882982</v>
       </c>
       <c r="P375" t="n">
         <v>2500</v>
@@ -16855,10 +16855,10 @@
         <v>1440</v>
       </c>
       <c r="N376" t="n">
-        <v>2122.1634778259</v>
+        <v>2122.1634756504</v>
       </c>
       <c r="O376" t="n">
-        <v>3055915.408069296</v>
+        <v>3055915.404936576</v>
       </c>
       <c r="P376" t="n">
         <v>2900</v>
@@ -16901,10 +16901,10 @@
         <v>396</v>
       </c>
       <c r="N377" t="n">
-        <v>2056.0820030996</v>
+        <v>2056.0819782355</v>
       </c>
       <c r="O377" t="n">
-        <v>814208.4732274417</v>
+        <v>814208.4633812581</v>
       </c>
       <c r="P377" t="n">
         <v>2900</v>
@@ -16947,10 +16947,10 @@
         <v>714</v>
       </c>
       <c r="N378" t="n">
-        <v>3224.5698459846</v>
+        <v>3224.5698785872</v>
       </c>
       <c r="O378" t="n">
-        <v>2302342.870033004</v>
+        <v>2302342.893311261</v>
       </c>
       <c r="P378" t="n">
         <v>4500</v>
@@ -16993,10 +16993,10 @@
         <v>864</v>
       </c>
       <c r="N379" t="n">
-        <v>1655.9292037471</v>
+        <v>1655.9291699295</v>
       </c>
       <c r="O379" t="n">
-        <v>1430722.832037495</v>
+        <v>1430722.802819088</v>
       </c>
       <c r="P379" t="n">
         <v>2500</v>
@@ -17993,10 +17993,10 @@
         <v>2</v>
       </c>
       <c r="N400" t="n">
-        <v>1538.0108069164</v>
+        <v>1530.4499180664</v>
       </c>
       <c r="O400" t="n">
-        <v>3076.0216138328</v>
+        <v>3060.8998361328</v>
       </c>
       <c r="P400" t="n">
         <v>2600</v>
@@ -18436,10 +18436,10 @@
         <v>1</v>
       </c>
       <c r="N410" t="n">
-        <v>1283.6525514403</v>
+        <v>1283.6523305085</v>
       </c>
       <c r="O410" t="n">
-        <v>1283.6525514403</v>
+        <v>1283.6523305085</v>
       </c>
       <c r="P410" t="n">
         <v>1900</v>
@@ -18617,10 +18617,10 @@
         <v>5844</v>
       </c>
       <c r="N414" t="n">
-        <v>517.29511103247</v>
+        <v>517.29522417328</v>
       </c>
       <c r="O414" t="n">
-        <v>3023072.628873755</v>
+        <v>3023073.290068648</v>
       </c>
       <c r="P414" t="n">
         <v>900</v>
@@ -18749,10 +18749,10 @@
         <v>14791</v>
       </c>
       <c r="N417" t="n">
-        <v>703.79473431536</v>
+        <v>703.79472483574</v>
       </c>
       <c r="O417" t="n">
-        <v>10409827.91525849</v>
+        <v>10409827.77504543</v>
       </c>
       <c r="P417" t="n">
         <v>900</v>
@@ -19326,10 +19326,10 @@
         <v>569</v>
       </c>
       <c r="N430" t="n">
-        <v>1595.4991666667</v>
+        <v>1595.4982940252</v>
       </c>
       <c r="O430" t="n">
-        <v>907839.0258333522</v>
+        <v>907838.5293003388</v>
       </c>
       <c r="P430" t="n">
         <v>2500</v>
@@ -20203,10 +20203,10 @@
         <v>1976</v>
       </c>
       <c r="N449" t="n">
-        <v>7046.9398267273</v>
+        <v>7046.9398265771</v>
       </c>
       <c r="O449" t="n">
-        <v>13924753.09761314</v>
+        <v>13924753.09731635</v>
       </c>
       <c r="P449" t="n">
         <v>9900</v>
@@ -20874,10 +20874,10 @@
         <v>357</v>
       </c>
       <c r="N464" t="n">
-        <v>6172.7748309179</v>
+        <v>6172.7748387097</v>
       </c>
       <c r="O464" t="n">
-        <v>2203680.61463769</v>
+        <v>2203680.617419363</v>
       </c>
       <c r="P464" t="n">
         <v>8000</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -6548,10 +6548,10 @@
         <v>864</v>
       </c>
       <c r="N145" t="n">
-        <v>12422.462959583</v>
+        <v>12422.46296087</v>
       </c>
       <c r="O145" t="n">
-        <v>10733007.99707971</v>
+        <v>10733007.99819168</v>
       </c>
       <c r="P145" t="n">
         <v>19900</v>
@@ -7970,10 +7970,10 @@
         <v>1248</v>
       </c>
       <c r="N177" t="n">
-        <v>2403.5207171448</v>
+        <v>2403.5207309746</v>
       </c>
       <c r="O177" t="n">
-        <v>2999593.854996711</v>
+        <v>2999593.872256301</v>
       </c>
       <c r="P177" t="n">
         <v>3500</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.855198556</v>
+        <v>6272.8552079566</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.722888096</v>
+        <v>1354936.724918626</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -2029,10 +2029,10 @@
         <v>144</v>
       </c>
       <c r="N41" t="n">
-        <v>3716.3301967213</v>
+        <v>3716.3301970443</v>
       </c>
       <c r="O41" t="n">
-        <v>535151.5483278672</v>
+        <v>535151.5483743792</v>
       </c>
       <c r="P41" t="n">
         <v>9500</v>
@@ -6062,10 +6062,10 @@
         <v>168</v>
       </c>
       <c r="N134" t="n">
-        <v>3594.2529307806</v>
+        <v>3594.2529255711</v>
       </c>
       <c r="O134" t="n">
-        <v>603834.4923711407</v>
+        <v>603834.4914959448</v>
       </c>
       <c r="P134" t="n">
         <v>6500</v>
@@ -6509,10 +6509,10 @@
         <v>864</v>
       </c>
       <c r="N144" t="n">
-        <v>12422.462986842</v>
+        <v>12422.462990777</v>
       </c>
       <c r="O144" t="n">
-        <v>10733008.02063149</v>
+        <v>10733008.02403133</v>
       </c>
       <c r="P144" t="n">
         <v>19900</v>
@@ -6738,10 +6738,10 @@
         <v>78</v>
       </c>
       <c r="N149" t="n">
-        <v>3041.6600148258</v>
+        <v>3041.6600148478</v>
       </c>
       <c r="O149" t="n">
-        <v>237249.4811564124</v>
+        <v>237249.4811581284</v>
       </c>
       <c r="P149" t="n">
         <v>5500</v>
@@ -7839,10 +7839,10 @@
         <v>768</v>
       </c>
       <c r="N174" t="n">
-        <v>1630.9246804626</v>
+        <v>1630.9246976176</v>
       </c>
       <c r="O174" t="n">
-        <v>1252550.154595277</v>
+        <v>1252550.167770317</v>
       </c>
       <c r="P174" t="n">
         <v>2500</v>
@@ -9919,10 +9919,10 @@
         <v>150</v>
       </c>
       <c r="N222" t="n">
-        <v>4285.1964141414</v>
+        <v>4285.1964303797</v>
       </c>
       <c r="O222" t="n">
-        <v>642779.4621212101</v>
+        <v>642779.464556955</v>
       </c>
       <c r="P222" t="n">
         <v>6900</v>
@@ -16540,10 +16540,10 @@
         <v>4224</v>
       </c>
       <c r="N369" t="n">
-        <v>1516.0387356204</v>
+        <v>1516.0387309278</v>
       </c>
       <c r="O369" t="n">
-        <v>6403747.61926057</v>
+        <v>6403747.599439028</v>
       </c>
       <c r="P369" t="n">
         <v>2300</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-23</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-24</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
@@ -795,19 +795,19 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="N10" t="n">
         <v>27000</v>
       </c>
       <c r="O10" t="n">
-        <v>1620000</v>
+        <v>1296000</v>
       </c>
       <c r="P10" t="n">
         <v>20000</v>
       </c>
       <c r="Q10" t="n">
-        <v>1200000</v>
+        <v>960000</v>
       </c>
     </row>
     <row r="11">
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3103165299</v>
+        <v>1811.3106796117</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.856975382</v>
+        <v>326035.922330106</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1514,10 +1514,10 @@
         <v>40</v>
       </c>
       <c r="N28" t="n">
-        <v>57762.968627451</v>
+        <v>57762.968613861</v>
       </c>
       <c r="O28" t="n">
-        <v>2310518.74509804</v>
+        <v>2310518.74455444</v>
       </c>
       <c r="P28" t="n">
         <v>87343</v>
@@ -1834,10 +1834,10 @@
         <v>216</v>
       </c>
       <c r="N36" t="n">
-        <v>6272.8552079566</v>
+        <v>6272.8552268603</v>
       </c>
       <c r="O36" t="n">
-        <v>1354936.724918626</v>
+        <v>1354936.729001825</v>
       </c>
       <c r="P36" t="n">
         <v>7900</v>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
@@ -2338,19 +2338,19 @@
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="N49" t="n">
         <v>31409.32</v>
       </c>
       <c r="O49" t="n">
-        <v>2041605.8</v>
+        <v>1287782.12</v>
       </c>
       <c r="P49" t="n">
         <v>45500</v>
       </c>
       <c r="Q49" t="n">
-        <v>2957500</v>
+        <v>1865500</v>
       </c>
     </row>
     <row r="50">
@@ -2542,10 +2542,10 @@
         <v>48</v>
       </c>
       <c r="N54" t="n">
-        <v>15711.963910256</v>
+        <v>15711.963831169</v>
       </c>
       <c r="O54" t="n">
-        <v>754174.2676922879</v>
+        <v>754174.263896112</v>
       </c>
       <c r="P54" t="n">
         <v>28500</v>
@@ -2636,10 +2636,10 @@
         <v>2</v>
       </c>
       <c r="N56" t="n">
-        <v>13712.833333333</v>
+        <v>13712.764</v>
       </c>
       <c r="O56" t="n">
-        <v>27425.666666666</v>
+        <v>27425.528</v>
       </c>
       <c r="P56" t="n">
         <v>22600</v>
@@ -3064,10 +3064,10 @@
         <v>2</v>
       </c>
       <c r="N66" t="n">
-        <v>174389.9</v>
+        <v>174389.98666667</v>
       </c>
       <c r="O66" t="n">
-        <v>348779.8</v>
+        <v>348779.97333334</v>
       </c>
       <c r="P66" t="n">
         <v>368200</v>
@@ -3336,7 +3336,7 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
@@ -3345,19 +3345,19 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="N72" t="n">
         <v>27000</v>
       </c>
       <c r="O72" t="n">
-        <v>1782000</v>
+        <v>1620000</v>
       </c>
       <c r="P72" t="n">
         <v>20000</v>
       </c>
       <c r="Q72" t="n">
-        <v>1320000</v>
+        <v>1200000</v>
       </c>
     </row>
     <row r="73">
@@ -3853,10 +3853,10 @@
         <v>480</v>
       </c>
       <c r="N84" t="n">
-        <v>1950.2137350835</v>
+        <v>1950.2137275986</v>
       </c>
       <c r="O84" t="n">
-        <v>936102.59284008</v>
+        <v>936102.589247328</v>
       </c>
       <c r="P84" t="n">
         <v>2900</v>
@@ -4836,10 +4836,10 @@
         <v>1080</v>
       </c>
       <c r="N107" t="n">
-        <v>2582.2549274255</v>
+        <v>2582.2549040675</v>
       </c>
       <c r="O107" t="n">
-        <v>2788835.32161954</v>
+        <v>2788835.2963929</v>
       </c>
       <c r="P107" t="n">
         <v>4500</v>
@@ -4928,10 +4928,10 @@
         <v>1619</v>
       </c>
       <c r="N109" t="n">
-        <v>5216.8958543674</v>
+        <v>5216.8958410068</v>
       </c>
       <c r="O109" t="n">
-        <v>8446154.388220821</v>
+        <v>8446154.366590008</v>
       </c>
       <c r="P109" t="n">
         <v>8500</v>
@@ -5020,10 +5020,10 @@
         <v>6298</v>
       </c>
       <c r="N111" t="n">
-        <v>3158.8608400976</v>
+        <v>3158.8608413965</v>
       </c>
       <c r="O111" t="n">
-        <v>19894505.57093468</v>
+        <v>19894505.57911516</v>
       </c>
       <c r="P111" t="n">
         <v>5600</v>
@@ -5066,10 +5066,10 @@
         <v>144</v>
       </c>
       <c r="N112" t="n">
-        <v>3841.6251265823</v>
+        <v>3841.6251483051</v>
       </c>
       <c r="O112" t="n">
-        <v>553194.0182278511</v>
+        <v>553194.0213559344</v>
       </c>
       <c r="P112" t="n">
         <v>6900</v>
@@ -5158,10 +5158,10 @@
         <v>224</v>
       </c>
       <c r="N114" t="n">
-        <v>2694.8230192308</v>
+        <v>2694.8229787234</v>
       </c>
       <c r="O114" t="n">
-        <v>603640.3563076992</v>
+        <v>603640.3472340415</v>
       </c>
       <c r="P114" t="n">
         <v>4900</v>
@@ -5432,10 +5432,10 @@
         <v>3024</v>
       </c>
       <c r="N120" t="n">
-        <v>3795.7100076292</v>
+        <v>3795.7100076321</v>
       </c>
       <c r="O120" t="n">
-        <v>11478227.0630707</v>
+        <v>11478227.06307947</v>
       </c>
       <c r="P120" t="n">
         <v>6200</v>
@@ -5873,7 +5873,7 @@
         </is>
       </c>
       <c r="J130" t="n">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="K130" t="n">
         <v>0</v>
@@ -5882,19 +5882,19 @@
         <v>0</v>
       </c>
       <c r="M130" t="n">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="N130" t="n">
         <v>8662</v>
       </c>
       <c r="O130" t="n">
-        <v>4339662</v>
+        <v>4270366</v>
       </c>
       <c r="P130" t="n">
         <v>14200</v>
       </c>
       <c r="Q130" t="n">
-        <v>7114200</v>
+        <v>7000600</v>
       </c>
     </row>
     <row r="131">
@@ -6062,10 +6062,10 @@
         <v>168</v>
       </c>
       <c r="N134" t="n">
-        <v>3594.2529255711</v>
+        <v>3594.252920354</v>
       </c>
       <c r="O134" t="n">
-        <v>603834.4914959448</v>
+        <v>603834.490619472</v>
       </c>
       <c r="P134" t="n">
         <v>6500</v>
@@ -6509,10 +6509,10 @@
         <v>864</v>
       </c>
       <c r="N144" t="n">
-        <v>12422.462990777</v>
+        <v>12422.462992091</v>
       </c>
       <c r="O144" t="n">
-        <v>10733008.02403133</v>
+        <v>10733008.02516662</v>
       </c>
       <c r="P144" t="n">
         <v>19900</v>
@@ -6633,7 +6633,7 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>4908</v>
+        <v>4824</v>
       </c>
       <c r="K147" t="n">
         <v>0</v>
@@ -6642,19 +6642,19 @@
         <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>4908</v>
+        <v>4824</v>
       </c>
       <c r="N147" t="n">
-        <v>3472.2762824732</v>
+        <v>3472.2762877567</v>
       </c>
       <c r="O147" t="n">
-        <v>17041931.99437847</v>
+        <v>16750260.81213832</v>
       </c>
       <c r="P147" t="n">
         <v>5900</v>
       </c>
       <c r="Q147" t="n">
-        <v>28957200</v>
+        <v>28461600</v>
       </c>
     </row>
     <row r="148">
@@ -6784,10 +6784,10 @@
         <v>809</v>
       </c>
       <c r="N150" t="n">
-        <v>4371.1712631292</v>
+        <v>4371.1712633877</v>
       </c>
       <c r="O150" t="n">
-        <v>3536277.551871523</v>
+        <v>3536277.552080649</v>
       </c>
       <c r="P150" t="n">
         <v>8900</v>
@@ -7839,10 +7839,10 @@
         <v>768</v>
       </c>
       <c r="N174" t="n">
-        <v>1630.9246976176</v>
+        <v>1630.9246990529</v>
       </c>
       <c r="O174" t="n">
-        <v>1252550.167770317</v>
+        <v>1252550.168872627</v>
       </c>
       <c r="P174" t="n">
         <v>2500</v>
@@ -7885,10 +7885,10 @@
         <v>3456</v>
       </c>
       <c r="N175" t="n">
-        <v>1550.1947406745</v>
+        <v>1550.1947552537</v>
       </c>
       <c r="O175" t="n">
-        <v>5357473.023771072</v>
+        <v>5357473.074156787</v>
       </c>
       <c r="P175" t="n">
         <v>2500</v>
@@ -7931,10 +7931,10 @@
         <v>1248</v>
       </c>
       <c r="N176" t="n">
-        <v>2403.5210828242</v>
+        <v>2403.5211979522</v>
       </c>
       <c r="O176" t="n">
-        <v>2999594.311364602</v>
+        <v>2999594.455044345</v>
       </c>
       <c r="P176" t="n">
         <v>3500</v>
@@ -9742,10 +9742,10 @@
         <v>2880</v>
       </c>
       <c r="N218" t="n">
-        <v>6207.9882238578</v>
+        <v>6207.9882231175</v>
       </c>
       <c r="O218" t="n">
-        <v>17879006.08471046</v>
+        <v>17879006.0825784</v>
       </c>
       <c r="P218" t="n">
         <v>9900</v>
@@ -10429,10 +10429,10 @@
         <v>2160</v>
       </c>
       <c r="N234" t="n">
-        <v>4814.2679256837</v>
+        <v>4814.2679250376</v>
       </c>
       <c r="O234" t="n">
-        <v>10398818.71947679</v>
+        <v>10398818.71808122</v>
       </c>
       <c r="P234" t="n">
         <v>9900</v>
@@ -10516,10 +10516,10 @@
         <v>150</v>
       </c>
       <c r="N236" t="n">
-        <v>11562.0384</v>
+        <v>11562.038395415</v>
       </c>
       <c r="O236" t="n">
-        <v>1734305.76</v>
+        <v>1734305.75931225</v>
       </c>
       <c r="P236" t="n">
         <v>18500</v>
@@ -11528,7 +11528,7 @@
         </is>
       </c>
       <c r="J260" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K260" t="n">
         <v>0</v>
@@ -11537,19 +11537,19 @@
         <v>0</v>
       </c>
       <c r="M260" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="N260" t="n">
         <v>21508</v>
       </c>
       <c r="O260" t="n">
-        <v>387144</v>
+        <v>215080</v>
       </c>
       <c r="P260" t="n">
         <v>36900</v>
       </c>
       <c r="Q260" t="n">
-        <v>664200</v>
+        <v>369000</v>
       </c>
     </row>
     <row r="261">
@@ -13053,10 +13053,10 @@
         <v>1145</v>
       </c>
       <c r="N293" t="n">
-        <v>1778.4728585462</v>
+        <v>1778.4728622951</v>
       </c>
       <c r="O293" t="n">
-        <v>2036351.423035399</v>
+        <v>2036351.427327889</v>
       </c>
       <c r="P293" t="n">
         <v>4900</v>
@@ -13835,10 +13835,10 @@
         <v>28</v>
       </c>
       <c r="N310" t="n">
-        <v>2252.2983673469</v>
+        <v>2252.3005544554</v>
       </c>
       <c r="O310" t="n">
-        <v>63064.3542857132</v>
+        <v>63064.4155247512</v>
       </c>
       <c r="P310" t="n">
         <v>3900</v>
@@ -14017,10 +14017,10 @@
         <v>864</v>
       </c>
       <c r="N314" t="n">
-        <v>2328.118653478</v>
+        <v>2328.1186430868</v>
       </c>
       <c r="O314" t="n">
-        <v>2011494.516604992</v>
+        <v>2011494.507626995</v>
       </c>
       <c r="P314" t="n">
         <v>4500</v>
@@ -15438,10 +15438,10 @@
         <v>192</v>
       </c>
       <c r="N345" t="n">
-        <v>17075.989518156</v>
+        <v>17075.98951782</v>
       </c>
       <c r="O345" t="n">
-        <v>3278589.987485952</v>
+        <v>3278589.98742144</v>
       </c>
       <c r="P345" t="n">
         <v>27500</v>
@@ -16068,7 +16068,7 @@
         </is>
       </c>
       <c r="J359" t="n">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="K359" t="n">
         <v>0</v>
@@ -16077,19 +16077,19 @@
         <v>0</v>
       </c>
       <c r="M359" t="n">
-        <v>356</v>
+        <v>330</v>
       </c>
       <c r="N359" t="n">
         <v>8700</v>
       </c>
       <c r="O359" t="n">
-        <v>3097200</v>
+        <v>2871000</v>
       </c>
       <c r="P359" t="n">
         <v>14900</v>
       </c>
       <c r="Q359" t="n">
-        <v>5304400</v>
+        <v>4917000</v>
       </c>
     </row>
     <row r="360">
@@ -16540,10 +16540,10 @@
         <v>4224</v>
       </c>
       <c r="N369" t="n">
-        <v>1516.0387309278</v>
+        <v>1516.0387272539</v>
       </c>
       <c r="O369" t="n">
-        <v>6403747.599439028</v>
+        <v>6403747.583920474</v>
       </c>
       <c r="P369" t="n">
         <v>2300</v>
@@ -16586,10 +16586,10 @@
         <v>288</v>
       </c>
       <c r="N370" t="n">
-        <v>2458.5123423754</v>
+        <v>2458.5123113728</v>
       </c>
       <c r="O370" t="n">
-        <v>708051.5546041152</v>
+        <v>708051.5456753664</v>
       </c>
       <c r="P370" t="n">
         <v>3500</v>
@@ -16724,10 +16724,10 @@
         <v>720</v>
       </c>
       <c r="N373" t="n">
-        <v>2079.3832679245</v>
+        <v>2079.3832653832</v>
       </c>
       <c r="O373" t="n">
-        <v>1497155.95290564</v>
+        <v>1497155.951075904</v>
       </c>
       <c r="P373" t="n">
         <v>2900</v>
@@ -16770,10 +16770,10 @@
         <v>672</v>
       </c>
       <c r="N374" t="n">
-        <v>1803.0172374039</v>
+        <v>1803.0172653236</v>
       </c>
       <c r="O374" t="n">
-        <v>1211627.583535421</v>
+        <v>1211627.602297459</v>
       </c>
       <c r="P374" t="n">
         <v>2500</v>
@@ -16816,10 +16816,10 @@
         <v>1440</v>
       </c>
       <c r="N375" t="n">
-        <v>2122.1634756504</v>
+        <v>2122.1634734735</v>
       </c>
       <c r="O375" t="n">
-        <v>3055915.404936576</v>
+        <v>3055915.40180184</v>
       </c>
       <c r="P375" t="n">
         <v>2900</v>
@@ -16862,10 +16862,10 @@
         <v>396</v>
       </c>
       <c r="N376" t="n">
-        <v>2056.0819719953</v>
+        <v>2056.0819217221</v>
       </c>
       <c r="O376" t="n">
-        <v>814208.4609101389</v>
+        <v>814208.4410019517</v>
       </c>
       <c r="P376" t="n">
         <v>2900</v>
@@ -16908,10 +16908,10 @@
         <v>714</v>
       </c>
       <c r="N377" t="n">
-        <v>3224.5698895028</v>
+        <v>3224.5699223947</v>
       </c>
       <c r="O377" t="n">
-        <v>2302342.901104999</v>
+        <v>2302342.924589816</v>
       </c>
       <c r="P377" t="n">
         <v>4500</v>
@@ -16954,10 +16954,10 @@
         <v>864</v>
       </c>
       <c r="N378" t="n">
-        <v>1655.929144427</v>
+        <v>1655.9291188041</v>
       </c>
       <c r="O378" t="n">
-        <v>1430722.780784928</v>
+        <v>1430722.758646742</v>
       </c>
       <c r="P378" t="n">
         <v>2500</v>
@@ -17267,7 +17267,7 @@
         </is>
       </c>
       <c r="J385" t="n">
-        <v>12096</v>
+        <v>11808</v>
       </c>
       <c r="K385" t="n">
         <v>0</v>
@@ -17276,19 +17276,19 @@
         <v>0</v>
       </c>
       <c r="M385" t="n">
-        <v>12096</v>
+        <v>11808</v>
       </c>
       <c r="N385" t="n">
         <v>1801</v>
       </c>
       <c r="O385" t="n">
-        <v>21784896</v>
+        <v>21266208</v>
       </c>
       <c r="P385" t="n">
         <v>2900</v>
       </c>
       <c r="Q385" t="n">
-        <v>35078400</v>
+        <v>34243200</v>
       </c>
     </row>
     <row r="386">
@@ -17954,10 +17954,10 @@
         <v>2</v>
       </c>
       <c r="N399" t="n">
-        <v>1530.4499180664</v>
+        <v>1530.4499179655</v>
       </c>
       <c r="O399" t="n">
-        <v>3060.8998361328</v>
+        <v>3060.899835931</v>
       </c>
       <c r="P399" t="n">
         <v>2600</v>
@@ -18222,10 +18222,10 @@
         <v>17</v>
       </c>
       <c r="N405" t="n">
-        <v>2286.164496124</v>
+        <v>2286.164453125</v>
       </c>
       <c r="O405" t="n">
-        <v>38864.796434108</v>
+        <v>38864.795703125</v>
       </c>
       <c r="P405" t="n">
         <v>3000</v>
@@ -18397,10 +18397,10 @@
         <v>1</v>
       </c>
       <c r="N409" t="n">
-        <v>1283.6523305085</v>
+        <v>1283.6520960699</v>
       </c>
       <c r="O409" t="n">
-        <v>1283.6523305085</v>
+        <v>1283.6520960699</v>
       </c>
       <c r="P409" t="n">
         <v>1900</v>
@@ -18578,10 +18578,10 @@
         <v>5844</v>
       </c>
       <c r="N413" t="n">
-        <v>517.29550190597</v>
+        <v>517.29583827893</v>
       </c>
       <c r="O413" t="n">
-        <v>3023074.913138489</v>
+        <v>3023076.878902067</v>
       </c>
       <c r="P413" t="n">
         <v>900</v>
@@ -18710,10 +18710,10 @@
         <v>14791</v>
       </c>
       <c r="N416" t="n">
-        <v>703.79470242023</v>
+        <v>703.79469605084</v>
       </c>
       <c r="O416" t="n">
-        <v>10409827.44349762</v>
+        <v>10409827.34928797</v>
       </c>
       <c r="P416" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3106796117</v>
+        <v>1811.3107843137</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.922330106</v>
+        <v>326035.941176466</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -5432,10 +5432,10 @@
         <v>3024</v>
       </c>
       <c r="N120" t="n">
-        <v>3795.7100076321</v>
+        <v>3795.710007638</v>
       </c>
       <c r="O120" t="n">
-        <v>11478227.06307947</v>
+        <v>11478227.06309731</v>
       </c>
       <c r="P120" t="n">
         <v>6200</v>
@@ -6195,10 +6195,10 @@
         <v>599</v>
       </c>
       <c r="N137" t="n">
-        <v>4891</v>
+        <v>4906.5393169182</v>
       </c>
       <c r="O137" t="n">
-        <v>2929709</v>
+        <v>2939017.050834002</v>
       </c>
       <c r="P137" t="n">
         <v>8200</v>
@@ -6645,10 +6645,10 @@
         <v>4824</v>
       </c>
       <c r="N147" t="n">
-        <v>3472.2762877567</v>
+        <v>3472.2762983503</v>
       </c>
       <c r="O147" t="n">
-        <v>16750260.81213832</v>
+        <v>16750260.86324185</v>
       </c>
       <c r="P147" t="n">
         <v>5900</v>
@@ -6784,10 +6784,10 @@
         <v>809</v>
       </c>
       <c r="N150" t="n">
-        <v>4371.1712633877</v>
+        <v>4371.171263905</v>
       </c>
       <c r="O150" t="n">
-        <v>3536277.552080649</v>
+        <v>3536277.552499145</v>
       </c>
       <c r="P150" t="n">
         <v>8900</v>
@@ -7839,10 +7839,10 @@
         <v>768</v>
       </c>
       <c r="N174" t="n">
-        <v>1630.9246990529</v>
+        <v>1630.9247048027</v>
       </c>
       <c r="O174" t="n">
-        <v>1252550.168872627</v>
+        <v>1252550.173288474</v>
       </c>
       <c r="P174" t="n">
         <v>2500</v>
@@ -7931,10 +7931,10 @@
         <v>1248</v>
       </c>
       <c r="N176" t="n">
-        <v>2403.5211979522</v>
+        <v>2403.5212124317</v>
       </c>
       <c r="O176" t="n">
-        <v>2999594.455044345</v>
+        <v>2999594.473114762</v>
       </c>
       <c r="P176" t="n">
         <v>3500</v>
@@ -9742,10 +9742,10 @@
         <v>2880</v>
       </c>
       <c r="N218" t="n">
-        <v>6207.9882231175</v>
+        <v>6213.167301168</v>
       </c>
       <c r="O218" t="n">
-        <v>17879006.0825784</v>
+        <v>17893921.82736384</v>
       </c>
       <c r="P218" t="n">
         <v>9900</v>
@@ -10470,10 +10470,10 @@
         <v>2329</v>
       </c>
       <c r="N235" t="n">
-        <v>3591.13</v>
+        <v>3594.9639466192</v>
       </c>
       <c r="O235" t="n">
-        <v>8363741.77</v>
+        <v>8372671.031676117</v>
       </c>
       <c r="P235" t="n">
         <v>6300</v>
@@ -13697,10 +13697,10 @@
         <v>576</v>
       </c>
       <c r="N307" t="n">
-        <v>8858.16</v>
+        <v>8873.1568848758</v>
       </c>
       <c r="O307" t="n">
-        <v>5102300.16</v>
+        <v>5110938.365688461</v>
       </c>
       <c r="P307" t="n">
         <v>15500</v>
@@ -14748,10 +14748,10 @@
         <v>1728</v>
       </c>
       <c r="N330" t="n">
-        <v>6849.2</v>
+        <v>6862.329456869</v>
       </c>
       <c r="O330" t="n">
-        <v>11835417.6</v>
+        <v>11858105.30146963</v>
       </c>
       <c r="P330" t="n">
         <v>11500</v>
@@ -16540,10 +16540,10 @@
         <v>4224</v>
       </c>
       <c r="N369" t="n">
-        <v>1516.0387272539</v>
+        <v>1516.0387269907</v>
       </c>
       <c r="O369" t="n">
-        <v>6403747.583920474</v>
+        <v>6403747.582808717</v>
       </c>
       <c r="P369" t="n">
         <v>2300</v>
@@ -16678,10 +16678,10 @@
         <v>288</v>
       </c>
       <c r="N372" t="n">
-        <v>1771.0893205318</v>
+        <v>1771.0891278195</v>
       </c>
       <c r="O372" t="n">
-        <v>510073.7243131584</v>
+        <v>510073.668812016</v>
       </c>
       <c r="P372" t="n">
         <v>2500</v>
@@ -16908,10 +16908,10 @@
         <v>714</v>
       </c>
       <c r="N377" t="n">
-        <v>3224.5699223947</v>
+        <v>3224.5699334073</v>
       </c>
       <c r="O377" t="n">
-        <v>2302342.924589816</v>
+        <v>2302342.932452812</v>
       </c>
       <c r="P377" t="n">
         <v>4500</v>
@@ -16954,10 +16954,10 @@
         <v>864</v>
       </c>
       <c r="N378" t="n">
-        <v>1655.9291188041</v>
+        <v>1655.9290150913</v>
       </c>
       <c r="O378" t="n">
-        <v>1430722.758646742</v>
+        <v>1430722.669038883</v>
       </c>
       <c r="P378" t="n">
         <v>2500</v>
@@ -18710,10 +18710,10 @@
         <v>14791</v>
       </c>
       <c r="N416" t="n">
-        <v>703.79469605084</v>
+        <v>703.79468467395</v>
       </c>
       <c r="O416" t="n">
-        <v>10409827.34928797</v>
+        <v>10409827.18101239</v>
       </c>
       <c r="P416" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-25</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-26</t>
         </is>
       </c>
     </row>
@@ -921,10 +921,10 @@
         <v>180</v>
       </c>
       <c r="N13" t="n">
-        <v>1811.3107843137</v>
+        <v>1811.3108241082</v>
       </c>
       <c r="O13" t="n">
-        <v>326035.941176466</v>
+        <v>326035.948339476</v>
       </c>
       <c r="P13" t="n">
         <v>2600</v>
@@ -1038,10 +1038,10 @@
         <v>244</v>
       </c>
       <c r="N16" t="n">
-        <v>3376.746386014</v>
+        <v>3376.7463829787</v>
       </c>
       <c r="O16" t="n">
-        <v>823926.118187416</v>
+        <v>823926.1174468028</v>
       </c>
       <c r="P16" t="n">
         <v>4500</v>
@@ -1834,10 +1834,10 @@
         <v>649</v>
       </c>
       <c r="N36" t="n">
-        <v>3926.8370726607</v>
+        <v>3926.8370711297</v>
       </c>
       <c r="O36" t="n">
-        <v>2548517.260156794</v>
+        <v>2548517.259163175</v>
       </c>
       <c r="P36" t="n">
         <v>4800</v>
@@ -1912,10 +1912,10 @@
         <v>527</v>
       </c>
       <c r="N38" t="n">
-        <v>2413.0010989011</v>
+        <v>2413.0011037528</v>
       </c>
       <c r="O38" t="n">
-        <v>1271651.57912088</v>
+        <v>1271651.581677726</v>
       </c>
       <c r="P38" t="n">
         <v>4700</v>
@@ -2461,10 +2461,10 @@
         <v>52</v>
       </c>
       <c r="N52" t="n">
-        <v>16486.406019417</v>
+        <v>16486.405882353</v>
       </c>
       <c r="O52" t="n">
-        <v>857293.113009684</v>
+        <v>857293.1058823559</v>
       </c>
       <c r="P52" t="n">
         <v>30500</v>
@@ -2503,10 +2503,10 @@
         <v>48</v>
       </c>
       <c r="N53" t="n">
-        <v>15711.96379085</v>
+        <v>15711.96375</v>
       </c>
       <c r="O53" t="n">
-        <v>754174.2619608</v>
+        <v>754174.26</v>
       </c>
       <c r="P53" t="n">
         <v>28500</v>
@@ -2636,10 +2636,10 @@
         <v>136</v>
       </c>
       <c r="N56" t="n">
-        <v>7407.7300564972</v>
+        <v>7407.7300571429</v>
       </c>
       <c r="O56" t="n">
-        <v>1007451.287683619</v>
+        <v>1007451.287771434</v>
       </c>
       <c r="P56" t="n">
         <v>10900</v>
@@ -2800,10 +2800,10 @@
         <v>20</v>
       </c>
       <c r="N60" t="n">
-        <v>56906.810555556</v>
+        <v>56906.812424242</v>
       </c>
       <c r="O60" t="n">
-        <v>1138136.21111112</v>
+        <v>1138136.24848484</v>
       </c>
       <c r="P60" t="n">
         <v>95900</v>
@@ -2847,10 +2847,10 @@
         <v>2</v>
       </c>
       <c r="N61" t="n">
-        <v>62349.638888889</v>
+        <v>62349.636470588</v>
       </c>
       <c r="O61" t="n">
-        <v>124699.277777778</v>
+        <v>124699.272941176</v>
       </c>
       <c r="P61" t="n">
         <v>109900</v>
@@ -4161,10 +4161,10 @@
         <v>244</v>
       </c>
       <c r="N91" t="n">
-        <v>21084.77148248</v>
+        <v>21084.771490515</v>
       </c>
       <c r="O91" t="n">
-        <v>5144684.24172512</v>
+        <v>5144684.24368566</v>
       </c>
       <c r="P91" t="n">
         <v>30000</v>
@@ -4755,10 +4755,10 @@
         <v>1080</v>
       </c>
       <c r="N105" t="n">
-        <v>2582.2548540429</v>
+        <v>2582.2548393782</v>
       </c>
       <c r="O105" t="n">
-        <v>2788835.242366332</v>
+        <v>2788835.226528456</v>
       </c>
       <c r="P105" t="n">
         <v>4500</v>
@@ -4939,10 +4939,10 @@
         <v>6298</v>
       </c>
       <c r="N109" t="n">
-        <v>3158.8608413965</v>
+        <v>3158.8608416484</v>
       </c>
       <c r="O109" t="n">
-        <v>19894505.57911516</v>
+        <v>19894505.58070162</v>
       </c>
       <c r="P109" t="n">
         <v>5600</v>
@@ -5625,10 +5625,10 @@
         <v>24</v>
       </c>
       <c r="N124" t="n">
-        <v>2267.0480857514</v>
+        <v>2267.048084922</v>
       </c>
       <c r="O124" t="n">
-        <v>54409.1540580336</v>
+        <v>54409.15403812799</v>
       </c>
       <c r="P124" t="n">
         <v>3900</v>
@@ -5981,10 +5981,10 @@
         <v>168</v>
       </c>
       <c r="N132" t="n">
-        <v>3594.2528624535</v>
+        <v>3594.2528571429</v>
       </c>
       <c r="O132" t="n">
-        <v>603834.4808921879</v>
+        <v>603834.4800000072</v>
       </c>
       <c r="P132" t="n">
         <v>6500</v>
@@ -6657,10 +6657,10 @@
         <v>78</v>
       </c>
       <c r="N147" t="n">
-        <v>3041.6600148588</v>
+        <v>3041.6600149031</v>
       </c>
       <c r="O147" t="n">
-        <v>237249.4811589864</v>
+        <v>237249.4811624418</v>
       </c>
       <c r="P147" t="n">
         <v>5500</v>
@@ -6703,10 +6703,10 @@
         <v>809</v>
       </c>
       <c r="N148" t="n">
-        <v>4371.1712639913</v>
+        <v>4371.1712646818</v>
       </c>
       <c r="O148" t="n">
-        <v>3536277.552568962</v>
+        <v>3536277.553127576</v>
       </c>
       <c r="P148" t="n">
         <v>8900</v>
@@ -7758,10 +7758,10 @@
         <v>768</v>
       </c>
       <c r="N172" t="n">
-        <v>1630.9247279434</v>
+        <v>1630.9248152786</v>
       </c>
       <c r="O172" t="n">
-        <v>1252550.191060531</v>
+        <v>1252550.258133965</v>
       </c>
       <c r="P172" t="n">
         <v>2500</v>
@@ -7804,10 +7804,10 @@
         <v>3456</v>
       </c>
       <c r="N173" t="n">
-        <v>1550.1948069948</v>
+        <v>1550.1948402243</v>
       </c>
       <c r="O173" t="n">
-        <v>5357473.252974029</v>
+        <v>5357473.367815181</v>
       </c>
       <c r="P173" t="n">
         <v>2500</v>
@@ -7850,10 +7850,10 @@
         <v>1248</v>
       </c>
       <c r="N174" t="n">
-        <v>2403.5220092133</v>
+        <v>2403.5223176428</v>
       </c>
       <c r="O174" t="n">
-        <v>2999595.467498198</v>
+        <v>2999595.852418214</v>
       </c>
       <c r="P174" t="n">
         <v>3500</v>
@@ -9354,10 +9354,10 @@
         <v>1254</v>
       </c>
       <c r="N209" t="n">
-        <v>880.3299232103</v>
+        <v>880.32993798065</v>
       </c>
       <c r="O209" t="n">
-        <v>1103933.723705716</v>
+        <v>1103933.742227735</v>
       </c>
       <c r="P209" t="n">
         <v>1200</v>
@@ -9661,10 +9661,10 @@
         <v>2729</v>
       </c>
       <c r="N216" t="n">
-        <v>6207.9882181666</v>
+        <v>6207.9882044083</v>
       </c>
       <c r="O216" t="n">
-        <v>16941599.84737665</v>
+        <v>16941599.80983025</v>
       </c>
       <c r="P216" t="n">
         <v>9900</v>
@@ -9838,10 +9838,10 @@
         <v>150</v>
       </c>
       <c r="N220" t="n">
-        <v>4285.1964713376</v>
+        <v>4285.196521181</v>
       </c>
       <c r="O220" t="n">
-        <v>642779.47070064</v>
+        <v>642779.47817715</v>
       </c>
       <c r="P220" t="n">
         <v>6900</v>
@@ -10348,10 +10348,10 @@
         <v>2110</v>
       </c>
       <c r="N232" t="n">
-        <v>4814.2679243911</v>
+        <v>4814.2679220172</v>
       </c>
       <c r="O232" t="n">
-        <v>10158105.32046522</v>
+        <v>10158105.31545629</v>
       </c>
       <c r="P232" t="n">
         <v>9900</v>
@@ -13754,10 +13754,10 @@
         <v>28</v>
       </c>
       <c r="N308" t="n">
-        <v>2252.3006175299</v>
+        <v>2252.300877551</v>
       </c>
       <c r="O308" t="n">
-        <v>63064.41729083721</v>
+        <v>63064.424571428</v>
       </c>
       <c r="P308" t="n">
         <v>3900</v>
@@ -13936,10 +13936,10 @@
         <v>864</v>
       </c>
       <c r="N312" t="n">
-        <v>2328.1186430868</v>
+        <v>2328.1186426504</v>
       </c>
       <c r="O312" t="n">
-        <v>2011494.507626995</v>
+        <v>2011494.507249946</v>
       </c>
       <c r="P312" t="n">
         <v>4500</v>
@@ -15357,10 +15357,10 @@
         <v>192</v>
       </c>
       <c r="N343" t="n">
-        <v>17075.989516129</v>
+        <v>17075.989515789</v>
       </c>
       <c r="O343" t="n">
-        <v>3278589.987096768</v>
+        <v>3278589.987031488</v>
       </c>
       <c r="P343" t="n">
         <v>27500</v>
@@ -16459,10 +16459,10 @@
         <v>4224</v>
       </c>
       <c r="N367" t="n">
-        <v>1516.0387126124</v>
+        <v>1516.0387122084</v>
       </c>
       <c r="O367" t="n">
-        <v>6403747.522074778</v>
+        <v>6403747.520368282</v>
       </c>
       <c r="P367" t="n">
         <v>2300</v>
@@ -16505,10 +16505,10 @@
         <v>288</v>
       </c>
       <c r="N368" t="n">
-        <v>2458.5122801183</v>
+        <v>2458.5122658275</v>
       </c>
       <c r="O368" t="n">
-        <v>708051.5366740704</v>
+        <v>708051.53255832</v>
       </c>
       <c r="P368" t="n">
         <v>3500</v>
@@ -16551,10 +16551,10 @@
         <v>240</v>
       </c>
       <c r="N369" t="n">
-        <v>1907.3924393064</v>
+        <v>1907.3924305556</v>
       </c>
       <c r="O369" t="n">
-        <v>457774.185433536</v>
+        <v>457774.183333344</v>
       </c>
       <c r="P369" t="n">
         <v>2500</v>
@@ -16597,10 +16597,10 @@
         <v>288</v>
       </c>
       <c r="N370" t="n">
-        <v>1771.0889280245</v>
+        <v>1771.0884872611</v>
       </c>
       <c r="O370" t="n">
-        <v>510073.611271056</v>
+        <v>510073.4843311968</v>
       </c>
       <c r="P370" t="n">
         <v>2500</v>
@@ -16643,10 +16643,10 @@
         <v>720</v>
       </c>
       <c r="N371" t="n">
-        <v>2079.383244983</v>
+        <v>2079.383183034</v>
       </c>
       <c r="O371" t="n">
-        <v>1497155.93638776</v>
+        <v>1497155.89178448</v>
       </c>
       <c r="P371" t="n">
         <v>2900</v>
@@ -16689,10 +16689,10 @@
         <v>672</v>
       </c>
       <c r="N372" t="n">
-        <v>1803.0173791902</v>
+        <v>1803.0174867491</v>
       </c>
       <c r="O372" t="n">
-        <v>1211627.678815814</v>
+        <v>1211627.751095395</v>
       </c>
       <c r="P372" t="n">
         <v>2500</v>
@@ -16735,10 +16735,10 @@
         <v>1440</v>
       </c>
       <c r="N373" t="n">
-        <v>2122.1634691152</v>
+        <v>2122.1634163581</v>
       </c>
       <c r="O373" t="n">
-        <v>3055915.395525888</v>
+        <v>3055915.319555664</v>
       </c>
       <c r="P373" t="n">
         <v>2900</v>
@@ -16781,10 +16781,10 @@
         <v>396</v>
       </c>
       <c r="N374" t="n">
-        <v>2056.081835443</v>
+        <v>2056.0813131313</v>
       </c>
       <c r="O374" t="n">
-        <v>814208.406835428</v>
+        <v>814208.1999999947</v>
       </c>
       <c r="P374" t="n">
         <v>2900</v>
@@ -16873,10 +16873,10 @@
         <v>864</v>
       </c>
       <c r="N376" t="n">
-        <v>1655.9289976134</v>
+        <v>1655.9289844683</v>
       </c>
       <c r="O376" t="n">
-        <v>1430722.653937978</v>
+        <v>1430722.642580611</v>
       </c>
       <c r="P376" t="n">
         <v>2500</v>
@@ -18497,10 +18497,10 @@
         <v>5844</v>
       </c>
       <c r="N411" t="n">
-        <v>517.29632575033</v>
+        <v>517.29643571978</v>
       </c>
       <c r="O411" t="n">
-        <v>3023079.727684929</v>
+        <v>3023080.370346394</v>
       </c>
       <c r="P411" t="n">
         <v>900</v>
@@ -18585,10 +18585,10 @@
         <v>5</v>
       </c>
       <c r="N413" t="n">
-        <v>3002.0210028653</v>
+        <v>3002.0210043042</v>
       </c>
       <c r="O413" t="n">
-        <v>15010.1050143265</v>
+        <v>15010.105021521</v>
       </c>
       <c r="P413" t="n">
         <v>4500</v>
@@ -18629,10 +18629,10 @@
         <v>14791</v>
       </c>
       <c r="N414" t="n">
-        <v>703.79465786602</v>
+        <v>703.79463731331</v>
       </c>
       <c r="O414" t="n">
-        <v>10409826.7844963</v>
+        <v>10409826.48050117</v>
       </c>
       <c r="P414" t="n">
         <v>900</v>
@@ -18678,10 +18678,10 @@
         <v>127</v>
       </c>
       <c r="N415" t="n">
-        <v>3182.2511342155</v>
+        <v>3182.2511650485</v>
       </c>
       <c r="O415" t="n">
-        <v>404145.8940453685</v>
+        <v>404145.8979611595</v>
       </c>
       <c r="P415" t="n">
         <v>6900</v>
@@ -19301,10 +19301,10 @@
         <v>122</v>
       </c>
       <c r="N429" t="n">
-        <v>6078.9926048565</v>
+        <v>6078.992616408</v>
       </c>
       <c r="O429" t="n">
-        <v>741637.0977924931</v>
+        <v>741637.099201776</v>
       </c>
       <c r="P429" t="n">
         <v>18500</v>
@@ -19853,10 +19853,10 @@
         <v>50</v>
       </c>
       <c r="N441" t="n">
-        <v>4159.0003007519</v>
+        <v>4159.0003030303</v>
       </c>
       <c r="O441" t="n">
-        <v>207950.015037595</v>
+        <v>207950.015151515</v>
       </c>
       <c r="P441" t="n">
         <v>8900</v>
@@ -20083,10 +20083,10 @@
         <v>1976</v>
       </c>
       <c r="N446" t="n">
-        <v>7046.9398263889</v>
+        <v>7046.9398263512</v>
       </c>
       <c r="O446" t="n">
-        <v>13924753.09694447</v>
+        <v>13924753.09686997</v>
       </c>
       <c r="P446" t="n">
         <v>9900</v>
@@ -22120,10 +22120,10 @@
         <v>1</v>
       </c>
       <c r="N493" t="n">
-        <v>4985.4075471698</v>
+        <v>4985.4083333333</v>
       </c>
       <c r="O493" t="n">
-        <v>4985.4075471698</v>
+        <v>4985.4083333333</v>
       </c>
       <c r="P493" t="n">
         <v>7900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -15677,10 +15677,10 @@
         <v>179</v>
       </c>
       <c r="N350" t="n">
-        <v>10755</v>
+        <v>10795.738636364</v>
       </c>
       <c r="O350" t="n">
-        <v>1925145</v>
+        <v>1932437.215909156</v>
       </c>
       <c r="P350" t="n">
         <v>17900</v>
@@ -18629,10 +18629,10 @@
         <v>14791</v>
       </c>
       <c r="N414" t="n">
-        <v>703.79463731331</v>
+        <v>703.79463559345</v>
       </c>
       <c r="O414" t="n">
-        <v>10409826.48050117</v>
+        <v>10409826.45506272</v>
       </c>
       <c r="P414" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -431,7 +431,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-27</t>
+          <t>Consolidado (costo desde Existencias Totales) generado el 2026-09-28</t>
         </is>
       </c>
     </row>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -798,10 +798,10 @@
         <v>48</v>
       </c>
       <c r="N10" t="n">
-        <v>27109.756097561</v>
+        <v>27000</v>
       </c>
       <c r="O10" t="n">
-        <v>1301268.292682928</v>
+        <v>1296000</v>
       </c>
       <c r="P10" t="n">
         <v>20000</v>
@@ -4714,10 +4714,10 @@
         <v>1080</v>
       </c>
       <c r="N104" t="n">
-        <v>2582.25476203</v>
+        <v>2586.3633253779</v>
       </c>
       <c r="O104" t="n">
-        <v>2788835.1429924</v>
+        <v>2793272.391408132</v>
       </c>
       <c r="P104" t="n">
         <v>4500</v>
@@ -6477,10 +6477,10 @@
         <v>4686</v>
       </c>
       <c r="N143" t="n">
-        <v>3472.2763744227</v>
+        <v>3472.276379862</v>
       </c>
       <c r="O143" t="n">
-        <v>16271087.09054477</v>
+        <v>16271087.11603333</v>
       </c>
       <c r="P143" t="n">
         <v>5900</v>
@@ -7717,10 +7717,10 @@
         <v>3071</v>
       </c>
       <c r="N171" t="n">
-        <v>1550.1950026961</v>
+        <v>1550.1949625568</v>
       </c>
       <c r="O171" t="n">
-        <v>4760648.853279723</v>
+        <v>4760648.730011933</v>
       </c>
       <c r="P171" t="n">
         <v>2500</v>
@@ -7763,10 +7763,10 @@
         <v>1248</v>
       </c>
       <c r="N172" t="n">
-        <v>2403.522961183</v>
+        <v>2403.5229357459</v>
       </c>
       <c r="O172" t="n">
-        <v>2999596.655556384</v>
+        <v>2999596.623810884</v>
       </c>
       <c r="P172" t="n">
         <v>3500</v>
@@ -8341,10 +8341,10 @@
         <v>90</v>
       </c>
       <c r="N185" t="n">
-        <v>17991.272727273</v>
+        <v>17328</v>
       </c>
       <c r="O185" t="n">
-        <v>1619214.54545457</v>
+        <v>1559520</v>
       </c>
       <c r="P185" t="n">
         <v>32900</v>
@@ -9354,10 +9354,10 @@
         <v>41</v>
       </c>
       <c r="N209" t="n">
-        <v>11724.722692308</v>
+        <v>11431.604487179</v>
       </c>
       <c r="O209" t="n">
-        <v>480713.630384628</v>
+        <v>468695.783974339</v>
       </c>
       <c r="P209" t="n">
         <v>48900</v>
@@ -9441,10 +9441,10 @@
         <v>144</v>
       </c>
       <c r="N211" t="n">
-        <v>30745.062773723</v>
+        <v>30611</v>
       </c>
       <c r="O211" t="n">
-        <v>4427289.039416112</v>
+        <v>4407984</v>
       </c>
       <c r="P211" t="n">
         <v>38900</v>
@@ -9574,10 +9574,10 @@
         <v>2641</v>
       </c>
       <c r="N214" t="n">
-        <v>6207.9882003658</v>
+        <v>6207.9882013781</v>
       </c>
       <c r="O214" t="n">
-        <v>16395296.83716608</v>
+        <v>16395296.83983956</v>
       </c>
       <c r="P214" t="n">
         <v>9900</v>
@@ -10261,10 +10261,10 @@
         <v>1988</v>
       </c>
       <c r="N230" t="n">
-        <v>4814.2633472037</v>
+        <v>4814.2633516301</v>
       </c>
       <c r="O230" t="n">
-        <v>9570755.534240955</v>
+        <v>9570755.543040639</v>
       </c>
       <c r="P230" t="n">
         <v>9900</v>
@@ -11034,10 +11034,10 @@
         <v>34</v>
       </c>
       <c r="N248" t="n">
-        <v>27123.764610526</v>
+        <v>27123.764587738</v>
       </c>
       <c r="O248" t="n">
-        <v>922207.9967578839</v>
+        <v>922207.9959830919</v>
       </c>
       <c r="P248" t="n">
         <v>44500</v>
@@ -12471,10 +12471,10 @@
         <v>1</v>
       </c>
       <c r="N280" t="n">
-        <v>10174</v>
+        <v>11021.833333333</v>
       </c>
       <c r="O280" t="n">
-        <v>10174</v>
+        <v>11021.833333333</v>
       </c>
       <c r="P280" t="n">
         <v>16900</v>
@@ -12931,10 +12931,10 @@
         <v>648</v>
       </c>
       <c r="N290" t="n">
-        <v>22935.194995686</v>
+        <v>22739</v>
       </c>
       <c r="O290" t="n">
-        <v>14862006.35720453</v>
+        <v>14734872</v>
       </c>
       <c r="P290" t="n">
         <v>36900</v>
@@ -14350,10 +14350,10 @@
         <v>25</v>
       </c>
       <c r="N321" t="n">
-        <v>21286.162162162</v>
+        <v>20726</v>
       </c>
       <c r="O321" t="n">
-        <v>532154.05405405</v>
+        <v>518150</v>
       </c>
       <c r="P321" t="n">
         <v>33900</v>
@@ -14994,10 +14994,10 @@
         <v>425</v>
       </c>
       <c r="N335" t="n">
-        <v>13585.998452012</v>
+        <v>13565</v>
       </c>
       <c r="O335" t="n">
-        <v>5774049.3421051</v>
+        <v>5765125</v>
       </c>
       <c r="P335" t="n">
         <v>22500</v>
@@ -15086,10 +15086,10 @@
         <v>120</v>
       </c>
       <c r="N337" t="n">
-        <v>19059.165545087</v>
+        <v>19008</v>
       </c>
       <c r="O337" t="n">
-        <v>2287099.86541044</v>
+        <v>2280960</v>
       </c>
       <c r="P337" t="n">
         <v>30900</v>
@@ -15178,10 +15178,10 @@
         <v>120</v>
       </c>
       <c r="N339" t="n">
-        <v>18038.854166667</v>
+        <v>17992</v>
       </c>
       <c r="O339" t="n">
-        <v>2164662.50000004</v>
+        <v>2159040</v>
       </c>
       <c r="P339" t="n">
         <v>28900</v>
@@ -15224,10 +15224,10 @@
         <v>192</v>
       </c>
       <c r="N340" t="n">
-        <v>17112.014810127</v>
+        <v>17075.989514768</v>
       </c>
       <c r="O340" t="n">
-        <v>3285506.843544384</v>
+        <v>3278589.986835456</v>
       </c>
       <c r="P340" t="n">
         <v>27500</v>
@@ -16050,10 +16050,10 @@
         <v>144</v>
       </c>
       <c r="N358" t="n">
-        <v>15602.016806723</v>
+        <v>15472</v>
       </c>
       <c r="O358" t="n">
-        <v>2246690.420168112</v>
+        <v>2227968</v>
       </c>
       <c r="P358" t="n">
         <v>25900</v>
@@ -16326,10 +16326,10 @@
         <v>4224</v>
       </c>
       <c r="N364" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386990066</v>
       </c>
       <c r="O364" t="n">
-        <v>6403747.457625409</v>
+        <v>6403747.464603879</v>
       </c>
       <c r="P364" t="n">
         <v>2300</v>
@@ -16418,10 +16418,10 @@
         <v>240</v>
       </c>
       <c r="N366" t="n">
-        <v>1907.3924305556</v>
+        <v>1907.3922142857</v>
       </c>
       <c r="O366" t="n">
-        <v>457774.183333344</v>
+        <v>457774.131428568</v>
       </c>
       <c r="P366" t="n">
         <v>2500</v>
@@ -16556,10 +16556,10 @@
         <v>672</v>
       </c>
       <c r="N369" t="n">
-        <v>1803.0176111361</v>
+        <v>1803.0176523702</v>
       </c>
       <c r="O369" t="n">
-        <v>1211627.834683459</v>
+        <v>1211627.862392774</v>
       </c>
       <c r="P369" t="n">
         <v>2500</v>
@@ -16602,10 +16602,10 @@
         <v>1440</v>
       </c>
       <c r="N370" t="n">
-        <v>2122.1634163581</v>
+        <v>2122.1634141414</v>
       </c>
       <c r="O370" t="n">
-        <v>3055915.319555664</v>
+        <v>3055915.316363616</v>
       </c>
       <c r="P370" t="n">
         <v>2900</v>
@@ -16694,10 +16694,10 @@
         <v>714</v>
       </c>
       <c r="N372" t="n">
-        <v>3224.5700336323</v>
+        <v>3224.5700392597</v>
       </c>
       <c r="O372" t="n">
-        <v>2302343.004013462</v>
+        <v>2302343.008031426</v>
       </c>
       <c r="P372" t="n">
         <v>4500</v>
@@ -16740,10 +16740,10 @@
         <v>864</v>
       </c>
       <c r="N373" t="n">
-        <v>1655.9287789047</v>
+        <v>1655.9286125978</v>
       </c>
       <c r="O373" t="n">
-        <v>1430722.464973661</v>
+        <v>1430722.321284499</v>
       </c>
       <c r="P373" t="n">
         <v>2500</v>
@@ -17596,10 +17596,10 @@
         <v>2370</v>
       </c>
       <c r="N391" t="n">
-        <v>8945.379999999999</v>
+        <v>8949.4124778362</v>
       </c>
       <c r="O391" t="n">
-        <v>21200550.6</v>
+        <v>21210107.57247179</v>
       </c>
       <c r="P391" t="n">
         <v>14900</v>
@@ -17962,10 +17962,10 @@
         <v>17</v>
       </c>
       <c r="N399" t="n">
-        <v>2286.1643873518</v>
+        <v>2286.164453125</v>
       </c>
       <c r="O399" t="n">
-        <v>38864.7945849806</v>
+        <v>38864.795703125</v>
       </c>
       <c r="P399" t="n">
         <v>3000</v>
@@ -18318,10 +18318,10 @@
         <v>4116</v>
       </c>
       <c r="N407" t="n">
-        <v>517.29691759113</v>
+        <v>517.29686746988</v>
       </c>
       <c r="O407" t="n">
-        <v>2129194.112805091</v>
+        <v>2129193.906506026</v>
       </c>
       <c r="P407" t="n">
         <v>900</v>
@@ -18450,10 +18450,10 @@
         <v>13063</v>
       </c>
       <c r="N410" t="n">
-        <v>703.79458866348</v>
+        <v>703.7945904135599</v>
       </c>
       <c r="O410" t="n">
-        <v>9193668.71171104</v>
+        <v>9193668.734572334</v>
       </c>
       <c r="P410" t="n">
         <v>900</v>

--- a/bodegas/CM-03.xlsx
+++ b/bodegas/CM-03.xlsx
@@ -2136,10 +2136,10 @@
         <v>30</v>
       </c>
       <c r="N44" t="n">
-        <v>21333.69</v>
+        <v>21425.250901288</v>
       </c>
       <c r="O44" t="n">
-        <v>640010.7</v>
+        <v>642757.52703864</v>
       </c>
       <c r="P44" t="n">
         <v>30000</v>
@@ -3140,10 +3140,10 @@
         <v>52</v>
       </c>
       <c r="N67" t="n">
-        <v>27000</v>
+        <v>28500</v>
       </c>
       <c r="O67" t="n">
-        <v>1404000</v>
+        <v>1482000</v>
       </c>
       <c r="P67" t="n">
         <v>20000</v>
@@ -4628,10 +4628,10 @@
         <v>1080</v>
       </c>
       <c r="N102" t="n">
-        <v>2582.2547091633</v>
+        <v>2582.2546851654</v>
       </c>
       <c r="O102" t="n">
-        <v>2788835.085896364</v>
+        <v>2788835.059978632</v>
       </c>
       <c r="P102" t="n">
         <v>4500</v>
@@ -5984,10 +5984,10 @@
         <v>337</v>
       </c>
       <c r="N132" t="n">
-        <v>14822.378814083</v>
+        <v>14831.53974042</v>
       </c>
       <c r="O132" t="n">
-        <v>4995141.660345971</v>
+        <v>4998228.89252154</v>
       </c>
       <c r="P132" t="n">
         <v>24900</v>
@@ -6206,10 +6206,10 @@
         <v>816</v>
       </c>
       <c r="N137" t="n">
-        <v>12422.46300928</v>
+        <v>12422.463013274</v>
       </c>
       <c r="O137" t="n">
-        <v>10136729.81557248</v>
+        <v>10136729.81883158</v>
       </c>
       <c r="P137" t="n">
         <v>19900</v>
@@ -6342,10 +6342,10 @@
         <v>4686</v>
       </c>
       <c r="N140" t="n">
-        <v>3472.276393501</v>
+        <v>3472.2764071985</v>
       </c>
       <c r="O140" t="n">
-        <v>16271087.17994568</v>
+        <v>16271087.24413217</v>
       </c>
       <c r="P140" t="n">
         <v>5900</v>
@@ -6481,10 +6481,10 @@
         <v>809</v>
       </c>
       <c r="N143" t="n">
-        <v>4371.1729731899</v>
+        <v>4371.1729736673</v>
       </c>
       <c r="O143" t="n">
-        <v>3536278.935310629</v>
+        <v>3536278.935696845</v>
       </c>
       <c r="P143" t="n">
         <v>8900</v>
@@ -7536,10 +7536,10 @@
         <v>384</v>
       </c>
       <c r="N167" t="n">
-        <v>1630.9251335113</v>
+        <v>1633.1055147059</v>
       </c>
       <c r="O167" t="n">
-        <v>626275.2512683391</v>
+        <v>627112.5176470657</v>
       </c>
       <c r="P167" t="n">
         <v>2500</v>
@@ -7582,10 +7582,10 @@
         <v>3071</v>
       </c>
       <c r="N168" t="n">
-        <v>1550.1949625568</v>
+        <v>1550.1949638844</v>
       </c>
       <c r="O168" t="n">
-        <v>4760648.730011933</v>
+        <v>4760648.734088993</v>
       </c>
       <c r="P168" t="n">
         <v>2500</v>
@@ -7628,10 +7628,10 @@
         <v>1248</v>
       </c>
       <c r="N169" t="n">
-        <v>2403.523063498</v>
+        <v>2404.4159026746</v>
       </c>
       <c r="O169" t="n">
-        <v>2999596.783245504</v>
+        <v>3000711.046537901</v>
       </c>
       <c r="P169" t="n">
         <v>3500</v>
@@ -10126,10 +10126,10 @@
         <v>1988</v>
       </c>
       <c r="N227" t="n">
-        <v>4814.2633494176</v>
+        <v>4814.2633472037</v>
       </c>
       <c r="O227" t="n">
-        <v>9570755.538642189</v>
+        <v>9570755.534240955</v>
       </c>
       <c r="P227" t="n">
         <v>7900</v>
@@ -10899,10 +10899,10 @@
         <v>34</v>
       </c>
       <c r="N245" t="n">
-        <v>27123.764587738</v>
+        <v>27123.764576271</v>
       </c>
       <c r="O245" t="n">
-        <v>922207.9959830919</v>
+        <v>922207.9955932141</v>
       </c>
       <c r="P245" t="n">
         <v>44500</v>
@@ -11283,10 +11283,10 @@
         <v>78</v>
       </c>
       <c r="N254" t="n">
-        <v>12981.59</v>
+        <v>13033.935120968</v>
       </c>
       <c r="O254" t="n">
-        <v>1012564.02</v>
+        <v>1016646.939435504</v>
       </c>
       <c r="P254" t="n">
         <v>21900</v>
@@ -12888,10 +12888,10 @@
         <v>648</v>
       </c>
       <c r="N289" t="n">
-        <v>25534</v>
+        <v>25577.697661152</v>
       </c>
       <c r="O289" t="n">
-        <v>16546032</v>
+        <v>16574348.0844265</v>
       </c>
       <c r="P289" t="n">
         <v>40900</v>
@@ -13806,10 +13806,10 @@
         <v>108</v>
       </c>
       <c r="N309" t="n">
-        <v>9003</v>
+        <v>9018.1565656566</v>
       </c>
       <c r="O309" t="n">
-        <v>972324</v>
+        <v>973960.9090909128</v>
       </c>
       <c r="P309" t="n">
         <v>14900</v>
@@ -14951,10 +14951,10 @@
         <v>120</v>
       </c>
       <c r="N334" t="n">
-        <v>17992</v>
+        <v>18015.518954248</v>
       </c>
       <c r="O334" t="n">
-        <v>2159040</v>
+        <v>2161862.27450976</v>
       </c>
       <c r="P334" t="n">
         <v>28900</v>
@@ -15639,10 +15639,10 @@
         <v>330</v>
       </c>
       <c r="N349" t="n">
-        <v>8700</v>
+        <v>8711.0687022901</v>
       </c>
       <c r="O349" t="n">
-        <v>2871000</v>
+        <v>2874652.671755733</v>
       </c>
       <c r="P349" t="n">
         <v>14900</v>
@@ -15823,10 +15823,10 @@
         <v>144</v>
       </c>
       <c r="N353" t="n">
-        <v>15472</v>
+        <v>15516.07977208</v>
       </c>
       <c r="O353" t="n">
-        <v>2227968</v>
+        <v>2234315.48717952</v>
       </c>
       <c r="P353" t="n">
         <v>25900</v>
@@ -16099,10 +16099,10 @@
         <v>4224</v>
       </c>
       <c r="N359" t="n">
-        <v>1516.0386973545</v>
+        <v>1516.0386972166</v>
       </c>
       <c r="O359" t="n">
-        <v>6403747.457625409</v>
+        <v>6403747.457042919</v>
       </c>
       <c r="P359" t="n">
         <v>2300</v>
@@ -16191,10 +16191,10 @@
         <v>240</v>
       </c>
       <c r="N361" t="n">
-        <v>1907.3922142857</v>
+        <v>1909.6656257449</v>
       </c>
       <c r="O361" t="n">
-        <v>457774.131428568</v>
+        <v>458319.750178776</v>
       </c>
       <c r="P361" t="n">
         <v>2500</v>
@@ -16329,10 +16329,10 @@
         <v>672</v>
       </c>
       <c r="N364" t="n">
-        <v>1803.0176696833</v>
+        <v>1803.0176731553</v>
       </c>
       <c r="O364" t="n">
-        <v>1211627.874027178</v>
+        <v>1211627.876360361</v>
       </c>
       <c r="P364" t="n">
         <v>2500</v>
@@ -16982,10 +16982,10 @@
         <v>1350</v>
       </c>
       <c r="N378" t="n">
-        <v>13518</v>
+        <v>13521.774923206</v>
       </c>
       <c r="O378" t="n">
-        <v>18249300</v>
+        <v>18254396.1463281</v>
       </c>
       <c r="P378" t="n">
         <v>21900</v>
@@ -18223,10 +18223,10 @@
         <v>13063</v>
       </c>
       <c r="N405" t="n">
-        <v>703.79458486774</v>
+        <v>703.7945831140599</v>
       </c>
       <c r="O405" t="n">
-        <v>9193668.662127288</v>
+        <v>9193668.639218966</v>
       </c>
       <c r="P405" t="n">
         <v>900</v>
@@ -21670,10 +21670,10 @@
         <v>1</v>
       </c>
       <c r="N483" t="n">
-        <v>4985.4086330935</v>
+        <v>5058.1883211679</v>
       </c>
       <c r="O483" t="n">
-        <v>4985.4086330935</v>
+        <v>5058.1883211679</v>
       </c>
       <c r="P483" t="n">
         <v>7900</v>
